--- a/output/第10期計画_サービス見込量の算定.xlsx
+++ b/output/第10期計画_サービス見込量の算定.xlsx
@@ -3012,7 +3012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4149,8 +4149,512 @@
         </is>
       </c>
     </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>5　地域支援事業の量の中長期的な推計（法第117条第2項第3号）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="4" t="inlineStr"/>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>事業</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>単位</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>R6実績
+（3町計）</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>延ばし方</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>訪問型サービス（従前相当）　利用者実人数</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="E46" s="15" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="F46" s="15" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="G46" s="15" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>認定者数の伸び</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度実績を据え置いて延ばす</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>通所型サービス（従前相当）　利用者実人数</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="E47" s="15" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="F47" s="15" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="G47" s="15" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>認定者数の伸び</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度実績を据え置いて延ばす</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>通所型サービスA　利用者実人数</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>149</v>
+      </c>
+      <c r="E48" s="15" t="n">
+        <v>155.3</v>
+      </c>
+      <c r="F48" s="15" t="n">
+        <v>167.3</v>
+      </c>
+      <c r="G48" s="15" t="n">
+        <v>171.8</v>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>認定者数の伸び</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度実績を据え置いて延ばす</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>通所型サービスC　利用者実人数</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E49" s="15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F49" s="15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G49" s="15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>認定者数の伸び</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度実績を据え置いて延ばす</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>その他生活支援（配食）　利用者実人数</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="E50" s="15" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="F50" s="15" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="G50" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>認定者数の伸び</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度実績を据え置いて延ばす</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>その他生活支援（複合的提供）　利用者実人数</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F51" s="15" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="G51" s="15" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>認定者数の伸び</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度実績を据え置いて延ばす</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>介護予防ケアマネジメントA　実施件数</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>件</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>199</v>
+      </c>
+      <c r="E52" s="15" t="n">
+        <v>207.4</v>
+      </c>
+      <c r="F52" s="15" t="n">
+        <v>223.5</v>
+      </c>
+      <c r="G52" s="15" t="n">
+        <v>229.5</v>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>認定者数の伸び</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度実績を据え置いて延ばす</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>介護予防ケアマネジメントC　実施件数</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>件</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="E53" s="15" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="F53" s="15" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="G53" s="15" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>認定者数の伸び</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度実績を据え置いて延ばす</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>基本チェックリスト実施者数</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>242</v>
+      </c>
+      <c r="E54" s="15" t="n">
+        <v>245.3</v>
+      </c>
+      <c r="F54" s="15" t="n">
+        <v>246.3</v>
+      </c>
+      <c r="G54" s="15" t="n">
+        <v>252.7</v>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>第1号被保険者数の伸び</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度実績を据え置いて延ばす</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>通いの場　箇所数</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>箇所</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E55" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="F55" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="G55" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>据え置き</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度実績を据え置いて延ばす</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>通いの場　参加者実人数</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>330</v>
+      </c>
+      <c r="E56" s="15" t="n">
+        <v>334.5</v>
+      </c>
+      <c r="F56" s="15" t="n">
+        <v>335.8</v>
+      </c>
+      <c r="G56" s="15" t="n">
+        <v>344.6</v>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>第1号被保険者数の伸び</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度実績を据え置いて延ばす</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>通いの場　週1回以上の箇所数</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>箇所</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E57" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="F57" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G57" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>据え置き</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度実績を据え置いて延ばす</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="56" customHeight="1">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>注1）延ばし方は1及び2の表と同じです。認定者数は令和22年度にかけて増えるためサービス事業の量も増え、第1号被保険者数はおおむね横ばいであるため一般介護予防事業の量は横ばいとなります。
+注2）事業費の中長期的な推計は、令和7年度の事業ごとの実績及び特定地域居宅サービス等事業その他の令和9年度に創設される事業の費用の額が定まった時点で算定します［要協議］。
+注3）通いの場の箇所数は3町の事業計画によるため据え置いています。中長期の目標値は3町と協議のうえ定めます［要協議］。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="31">
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="E28:G28"/>
     <mergeCell ref="C30:D30"/>
@@ -4174,6 +4678,8 @@
     <mergeCell ref="E25:G25"/>
     <mergeCell ref="E32:G32"/>
     <mergeCell ref="C27:D27"/>
+    <mergeCell ref="A44:I44"/>
+    <mergeCell ref="A58:I58"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="E33:G33"/>
     <mergeCell ref="A1:I1"/>

--- a/output/第10期計画_サービス見込量の算定.xlsx
+++ b/output/第10期計画_サービス見込量の算定.xlsx
@@ -191,7 +191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -275,6 +275,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
@@ -3012,7 +3018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4644,22 +4650,427 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="56" customHeight="1">
+    <row r="58" ht="42" customHeight="1">
       <c r="A58" s="10" t="inlineStr">
         <is>
           <t>注1）延ばし方は1及び2の表と同じです。認定者数は令和22年度にかけて増えるためサービス事業の量も増え、第1号被保険者数はおおむね横ばいであるため一般介護予防事業の量は横ばいとなります。
-注2）事業費の中長期的な推計は、令和7年度の事業ごとの実績及び特定地域居宅サービス等事業その他の令和9年度に創設される事業の費用の額が定まった時点で算定します［要協議］。
-注3）通いの場の箇所数は3町の事業計画によるため据え置いています。中長期の目標値は3町と協議のうえ定めます［要協議］。</t>
+注2）通いの場の箇所数は3町の事業計画によるため据え置いています。中長期の目標値は3町と協議のうえ定めます［要協議］。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>6　地域支援事業費の推計（見える化システムへの入力値）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="32" customHeight="1">
+      <c r="A61" s="4" t="inlineStr"/>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>単位</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>R6実績</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>延ばし方</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="32" customHeight="1">
+      <c r="A62" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>介護予防・日常生活支援総合事業費</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="D62" s="31" t="n">
+        <v>107129318</v>
+      </c>
+      <c r="E62" s="31" t="n">
+        <v>107129318</v>
+      </c>
+      <c r="F62" s="31" t="n">
+        <v>107129318</v>
+      </c>
+      <c r="G62" s="31" t="n">
+        <v>107129318</v>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>認定者数の伸び</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>第10期は令和6年度の水準を据え置く</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="32" customHeight="1">
+      <c r="A63" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>包括的支援事業（地域包括支援センターの運営）及び任意事業費並びに包括的支援事業（社会保障充実分）</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="D63" s="31" t="n">
+        <v>70031941</v>
+      </c>
+      <c r="E63" s="31" t="n">
+        <v>70031941</v>
+      </c>
+      <c r="F63" s="31" t="n">
+        <v>70031941</v>
+      </c>
+      <c r="G63" s="31" t="n">
+        <v>70031941</v>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>第1号被保険者数の伸び</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>第10期は令和6年度の水準を据え置く</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="32" customHeight="1">
+      <c r="A64" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>地域支援事業費（計）</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="D64" s="32" t="n">
+        <v>177161259</v>
+      </c>
+      <c r="E64" s="32" t="n">
+        <v>177161259</v>
+      </c>
+      <c r="F64" s="32" t="n">
+        <v>177161259</v>
+      </c>
+      <c r="G64" s="32" t="n">
+        <v>177161259</v>
+      </c>
+      <c r="H64" s="8" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I64" s="8" t="inlineStr">
+        <is>
+          <t>第10期は令和6年度の水準を据え置く</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="32" customHeight="1">
+      <c r="A66" s="4" t="inlineStr"/>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>単位</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>R6実績</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>令和12年度</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr"/>
+      <c r="I66" s="4" t="inlineStr"/>
+    </row>
+    <row r="67" ht="32" customHeight="1">
+      <c r="A67" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>介護予防・日常生活支援総合事業費</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="D67" s="31" t="n">
+        <v>107129318</v>
+      </c>
+      <c r="E67" s="31" t="n">
+        <v>112479138</v>
+      </c>
+      <c r="F67" s="31" t="n">
+        <v>120299137</v>
+      </c>
+      <c r="G67" s="31" t="n">
+        <v>123552614</v>
+      </c>
+      <c r="H67" s="6" t="inlineStr"/>
+      <c r="I67" s="6" t="inlineStr"/>
+    </row>
+    <row r="68" ht="32" customHeight="1">
+      <c r="A68" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>包括的支援事業（地域包括支援センターの運営）及び任意事業費並びに包括的支援事業（社会保障充実分）</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="D68" s="31" t="n">
+        <v>70031941</v>
+      </c>
+      <c r="E68" s="31" t="n">
+        <v>70967498</v>
+      </c>
+      <c r="F68" s="31" t="n">
+        <v>71263644</v>
+      </c>
+      <c r="G68" s="31" t="n">
+        <v>73123779</v>
+      </c>
+      <c r="H68" s="6" t="inlineStr"/>
+      <c r="I68" s="6" t="inlineStr"/>
+    </row>
+    <row r="69" ht="32" customHeight="1">
+      <c r="A69" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>地域支援事業費（計）</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>177161259</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>183446636</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>191562781</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>196676393</v>
+      </c>
+      <c r="H69" s="8" t="inlineStr"/>
+      <c r="I69" s="8" t="inlineStr"/>
+    </row>
+    <row r="71" ht="32" customHeight="1">
+      <c r="A71" s="4" t="inlineStr"/>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>単位</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>R6実績</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>令和27年度</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>令和32年度</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr"/>
+      <c r="H71" s="4" t="inlineStr"/>
+      <c r="I71" s="4" t="inlineStr"/>
+    </row>
+    <row r="72" ht="32" customHeight="1">
+      <c r="A72" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>介護予防・日常生活支援総合事業費</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="D72" s="31" t="n">
+        <v>107129318</v>
+      </c>
+      <c r="E72" s="31" t="n">
+        <v>118576472</v>
+      </c>
+      <c r="F72" s="31" t="n">
+        <v>118244825</v>
+      </c>
+      <c r="G72" s="6" t="inlineStr"/>
+      <c r="H72" s="6" t="inlineStr"/>
+      <c r="I72" s="6" t="inlineStr"/>
+    </row>
+    <row r="73" ht="32" customHeight="1">
+      <c r="A73" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>包括的支援事業（地域包括支援センターの運営）及び任意事業費並びに包括的支援事業（社会保障充実分）</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="D73" s="31" t="n">
+        <v>70031941</v>
+      </c>
+      <c r="E73" s="31" t="n">
+        <v>72382081</v>
+      </c>
+      <c r="F73" s="31" t="n">
+        <v>70317509</v>
+      </c>
+      <c r="G73" s="6" t="inlineStr"/>
+      <c r="H73" s="6" t="inlineStr"/>
+      <c r="I73" s="6" t="inlineStr"/>
+    </row>
+    <row r="74" ht="32" customHeight="1">
+      <c r="A74" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>地域支援事業費（計）</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>円</t>
+        </is>
+      </c>
+      <c r="D74" s="32" t="n">
+        <v>177161259</v>
+      </c>
+      <c r="E74" s="32" t="n">
+        <v>190958553</v>
+      </c>
+      <c r="F74" s="32" t="n">
+        <v>188562334</v>
+      </c>
+      <c r="G74" s="8" t="inlineStr"/>
+      <c r="H74" s="8" t="inlineStr"/>
+      <c r="I74" s="8" t="inlineStr"/>
+    </row>
+    <row r="75" ht="104" customHeight="1">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>注1）第10期（令和9年度から令和11年度まで）は令和6年度決算の水準を据え置いています。中長期は量の見込みと同じ伸び（総合事業費は認定者数、そのほかは第1号被保険者数）で延ばしました。
+注2）群ごとに分けているのは、調整交付金相当額及び調整交付金見込額の算定基礎に「介護予防・日常生活支援総合事業費」のみが入るためです。計をまとめて1つの事業に置くと調整交付金の額が変わります。
+注3）第10期も同じ伸びで延ばすと令和9年度179,819,930円・令和10年度181,201,294円・令和11年度182,617,622円となり、3か年で543,638,847円（据え置きとの差12,155,070円）です。保険料を上げる向きであり、据え置きは保険料が不足する側に誤る置き方です［要協議］。
+注4）令和9年4月に創設される特定地域居宅サービス等事業及び介護情報利活用事業は、費用の額が定まっていないため0として置いています（確認事項No.115・No.185）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="33">
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="E28:G28"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A75:I75"/>
     <mergeCell ref="E31:G31"/>
     <mergeCell ref="E34:G34"/>
     <mergeCell ref="E30:G30"/>
@@ -4682,6 +5093,7 @@
     <mergeCell ref="A58:I58"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="E33:G33"/>
+    <mergeCell ref="A60:I60"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E29:G29"/>
@@ -6411,7 +6823,7 @@
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="31" t="n">
+      <c r="A6" s="33" t="n">
         <v>1</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -6434,10 +6846,10 @@
           <t>3,044,598,937</t>
         </is>
       </c>
-      <c r="F6" s="31" t="n">
+      <c r="F6" s="33" t="n">
         <v>9035.1</v>
       </c>
-      <c r="G6" s="31" t="n">
+      <c r="G6" s="33" t="n">
         <v>6438</v>
       </c>
       <c r="H6" s="9" t="inlineStr">

--- a/output/第10期計画_サービス見込量の算定.xlsx
+++ b/output/第10期計画_サービス見込量の算定.xlsx
@@ -191,7 +191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -243,6 +243,18 @@
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
@@ -252,14 +264,8 @@
     <xf numFmtId="166" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
@@ -282,6 +288,12 @@
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2342,7 +2354,7 @@
       <c r="G6" s="15" t="n">
         <v>163.1</v>
       </c>
-      <c r="H6" s="24" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>90.4％</t>
         </is>
@@ -2377,7 +2389,7 @@
       <c r="G7" s="15" t="n">
         <v>69.7</v>
       </c>
-      <c r="H7" s="27" t="inlineStr">
+      <c r="H7" s="29" t="inlineStr">
         <is>
           <t>99.9％</t>
         </is>
@@ -2412,7 +2424,7 @@
       <c r="G8" s="15" t="n">
         <v>157.5</v>
       </c>
-      <c r="H8" s="24" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>58.4％</t>
         </is>
@@ -2447,7 +2459,7 @@
       <c r="G9" s="15" t="n">
         <v>71.3</v>
       </c>
-      <c r="H9" s="24" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>41.1％</t>
         </is>
@@ -2482,7 +2494,7 @@
       <c r="G10" s="15" t="n">
         <v>95.90000000000001</v>
       </c>
-      <c r="H10" s="24" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>86.1％</t>
         </is>
@@ -2670,7 +2682,7 @@
       <c r="C18" s="15" t="n">
         <v>505.6</v>
       </c>
-      <c r="D18" s="28" t="n">
+      <c r="D18" s="30" t="n">
         <v>0.4</v>
       </c>
       <c r="E18" s="15" t="n">
@@ -2705,7 +2717,7 @@
       <c r="C19" s="15" t="n">
         <v>547.2</v>
       </c>
-      <c r="D19" s="28" t="n">
+      <c r="D19" s="30" t="n">
         <v>5.6</v>
       </c>
       <c r="E19" s="15" t="n">
@@ -2740,7 +2752,7 @@
       <c r="C20" s="15" t="n">
         <v>563.9</v>
       </c>
-      <c r="D20" s="28" t="n">
+      <c r="D20" s="30" t="n">
         <v>10.8</v>
       </c>
       <c r="E20" s="15" t="n">
@@ -2775,7 +2787,7 @@
       <c r="C21" s="15" t="n">
         <v>538.4</v>
       </c>
-      <c r="D21" s="28" t="n">
+      <c r="D21" s="30" t="n">
         <v>4.5</v>
       </c>
       <c r="E21" s="15" t="n">
@@ -2810,7 +2822,7 @@
       <c r="C22" s="15" t="n">
         <v>535.2</v>
       </c>
-      <c r="D22" s="28" t="n">
+      <c r="D22" s="30" t="n">
         <v>4.1</v>
       </c>
       <c r="E22" s="15" t="n">
@@ -3652,14 +3664,14 @@
           <t>訪問介護相当サービス</t>
         </is>
       </c>
-      <c r="D25" s="29" t="n"/>
+      <c r="D25" s="31" t="n"/>
       <c r="E25" s="6" t="inlineStr">
         <is>
           <t>332人（延）</t>
         </is>
       </c>
-      <c r="F25" s="30" t="n"/>
-      <c r="G25" s="29" t="n"/>
+      <c r="F25" s="32" t="n"/>
+      <c r="G25" s="31" t="n"/>
       <c r="H25" s="6" t="inlineStr">
         <is>
           <t>延べ人数</t>
@@ -3685,14 +3697,14 @@
           <t>通所介護相当サービス</t>
         </is>
       </c>
-      <c r="D26" s="29" t="n"/>
+      <c r="D26" s="31" t="n"/>
       <c r="E26" s="6" t="inlineStr">
         <is>
           <t>375人（延）</t>
         </is>
       </c>
-      <c r="F26" s="30" t="n"/>
-      <c r="G26" s="29" t="n"/>
+      <c r="F26" s="32" t="n"/>
+      <c r="G26" s="31" t="n"/>
       <c r="H26" s="6" t="inlineStr">
         <is>
           <t>延べ人数</t>
@@ -3718,14 +3730,14 @@
           <t>通所型サービスＡ（緩和した基準によるサービス）</t>
         </is>
       </c>
-      <c r="D27" s="29" t="n"/>
+      <c r="D27" s="31" t="n"/>
       <c r="E27" s="6" t="inlineStr">
         <is>
           <t>年143日／延べ1,173名</t>
         </is>
       </c>
-      <c r="F27" s="30" t="n"/>
-      <c r="G27" s="29" t="n"/>
+      <c r="F27" s="32" t="n"/>
+      <c r="G27" s="31" t="n"/>
       <c r="H27" s="6" t="inlineStr">
         <is>
           <t>延べ人数</t>
@@ -3751,14 +3763,14 @@
           <t>通所型サービスＡ（緩和した基準によるサービス）</t>
         </is>
       </c>
-      <c r="D28" s="29" t="n"/>
+      <c r="D28" s="31" t="n"/>
       <c r="E28" s="6" t="inlineStr">
         <is>
           <t>延1,197人</t>
         </is>
       </c>
-      <c r="F28" s="30" t="n"/>
-      <c r="G28" s="29" t="n"/>
+      <c r="F28" s="32" t="n"/>
+      <c r="G28" s="31" t="n"/>
       <c r="H28" s="6" t="inlineStr">
         <is>
           <t>延べ人数</t>
@@ -3784,14 +3796,14 @@
           <t>通所型サービスＡ（緩和した基準によるサービス）</t>
         </is>
       </c>
-      <c r="D29" s="29" t="n"/>
+      <c r="D29" s="31" t="n"/>
       <c r="E29" s="6" t="inlineStr">
         <is>
           <t>延344人</t>
         </is>
       </c>
-      <c r="F29" s="30" t="n"/>
-      <c r="G29" s="29" t="n"/>
+      <c r="F29" s="32" t="n"/>
+      <c r="G29" s="31" t="n"/>
       <c r="H29" s="6" t="inlineStr">
         <is>
           <t>延べ人数</t>
@@ -3817,14 +3829,14 @@
           <t>通所型サービスＡ（緩和した基準によるサービス）</t>
         </is>
       </c>
-      <c r="D30" s="29" t="n"/>
+      <c r="D30" s="31" t="n"/>
       <c r="E30" s="6" t="inlineStr">
         <is>
           <t>465人（延）</t>
         </is>
       </c>
-      <c r="F30" s="30" t="n"/>
-      <c r="G30" s="29" t="n"/>
+      <c r="F30" s="32" t="n"/>
+      <c r="G30" s="31" t="n"/>
       <c r="H30" s="6" t="inlineStr">
         <is>
           <t>延べ人数</t>
@@ -3850,14 +3862,14 @@
           <t>通所型サービスＣ（短期集中予防サービス）</t>
         </is>
       </c>
-      <c r="D31" s="29" t="n"/>
+      <c r="D31" s="31" t="n"/>
       <c r="E31" s="6" t="inlineStr">
         <is>
           <t>延0人</t>
         </is>
       </c>
-      <c r="F31" s="30" t="n"/>
-      <c r="G31" s="29" t="n"/>
+      <c r="F31" s="32" t="n"/>
+      <c r="G31" s="31" t="n"/>
       <c r="H31" s="6" t="inlineStr">
         <is>
           <t>延べ人数</t>
@@ -3883,14 +3895,14 @@
           <t>栄養改善を目的とした配食</t>
         </is>
       </c>
-      <c r="D32" s="29" t="n"/>
+      <c r="D32" s="31" t="n"/>
       <c r="E32" s="6" t="inlineStr">
         <is>
           <t>4,298人（延）</t>
         </is>
       </c>
-      <c r="F32" s="30" t="n"/>
-      <c r="G32" s="29" t="n"/>
+      <c r="F32" s="32" t="n"/>
+      <c r="G32" s="31" t="n"/>
       <c r="H32" s="6" t="inlineStr">
         <is>
           <t>延べ人数</t>
@@ -3916,14 +3928,14 @@
           <t>訪問型サービス・通所型サービスの一体的提供等</t>
         </is>
       </c>
-      <c r="D33" s="29" t="n"/>
+      <c r="D33" s="31" t="n"/>
       <c r="E33" s="6" t="inlineStr">
         <is>
           <t>延173人</t>
         </is>
       </c>
-      <c r="F33" s="30" t="n"/>
-      <c r="G33" s="29" t="n"/>
+      <c r="F33" s="32" t="n"/>
+      <c r="G33" s="31" t="n"/>
       <c r="H33" s="6" t="inlineStr">
         <is>
           <t>延べ人数</t>
@@ -3949,14 +3961,14 @@
           <t>（４）介護予防ケアマネジメント（第１号介護予防支援事業）</t>
         </is>
       </c>
-      <c r="D34" s="29" t="n"/>
+      <c r="D34" s="31" t="n"/>
       <c r="E34" s="6" t="inlineStr">
         <is>
           <t>1,035人（延）</t>
         </is>
       </c>
-      <c r="F34" s="30" t="n"/>
-      <c r="G34" s="29" t="n"/>
+      <c r="F34" s="32" t="n"/>
+      <c r="G34" s="31" t="n"/>
       <c r="H34" s="6" t="inlineStr">
         <is>
           <t>延べ人数</t>
@@ -4722,16 +4734,16 @@
           <t>円</t>
         </is>
       </c>
-      <c r="D62" s="31" t="n">
+      <c r="D62" s="33" t="n">
         <v>107129318</v>
       </c>
-      <c r="E62" s="31" t="n">
+      <c r="E62" s="33" t="n">
         <v>107129318</v>
       </c>
-      <c r="F62" s="31" t="n">
+      <c r="F62" s="33" t="n">
         <v>107129318</v>
       </c>
-      <c r="G62" s="31" t="n">
+      <c r="G62" s="33" t="n">
         <v>107129318</v>
       </c>
       <c r="H62" s="6" t="inlineStr">
@@ -4759,16 +4771,16 @@
           <t>円</t>
         </is>
       </c>
-      <c r="D63" s="31" t="n">
+      <c r="D63" s="33" t="n">
         <v>70031941</v>
       </c>
-      <c r="E63" s="31" t="n">
+      <c r="E63" s="33" t="n">
         <v>70031941</v>
       </c>
-      <c r="F63" s="31" t="n">
+      <c r="F63" s="33" t="n">
         <v>70031941</v>
       </c>
-      <c r="G63" s="31" t="n">
+      <c r="G63" s="33" t="n">
         <v>70031941</v>
       </c>
       <c r="H63" s="6" t="inlineStr">
@@ -4796,16 +4808,16 @@
           <t>円</t>
         </is>
       </c>
-      <c r="D64" s="32" t="n">
+      <c r="D64" s="34" t="n">
         <v>177161259</v>
       </c>
-      <c r="E64" s="32" t="n">
+      <c r="E64" s="34" t="n">
         <v>177161259</v>
       </c>
-      <c r="F64" s="32" t="n">
+      <c r="F64" s="34" t="n">
         <v>177161259</v>
       </c>
-      <c r="G64" s="32" t="n">
+      <c r="G64" s="34" t="n">
         <v>177161259</v>
       </c>
       <c r="H64" s="8" t="inlineStr">
@@ -4868,16 +4880,16 @@
           <t>円</t>
         </is>
       </c>
-      <c r="D67" s="31" t="n">
+      <c r="D67" s="33" t="n">
         <v>107129318</v>
       </c>
-      <c r="E67" s="31" t="n">
+      <c r="E67" s="33" t="n">
         <v>112479138</v>
       </c>
-      <c r="F67" s="31" t="n">
+      <c r="F67" s="33" t="n">
         <v>120299137</v>
       </c>
-      <c r="G67" s="31" t="n">
+      <c r="G67" s="33" t="n">
         <v>123552614</v>
       </c>
       <c r="H67" s="6" t="inlineStr"/>
@@ -4897,16 +4909,16 @@
           <t>円</t>
         </is>
       </c>
-      <c r="D68" s="31" t="n">
+      <c r="D68" s="33" t="n">
         <v>70031941</v>
       </c>
-      <c r="E68" s="31" t="n">
+      <c r="E68" s="33" t="n">
         <v>70967498</v>
       </c>
-      <c r="F68" s="31" t="n">
+      <c r="F68" s="33" t="n">
         <v>71263644</v>
       </c>
-      <c r="G68" s="31" t="n">
+      <c r="G68" s="33" t="n">
         <v>73123779</v>
       </c>
       <c r="H68" s="6" t="inlineStr"/>
@@ -4926,16 +4938,16 @@
           <t>円</t>
         </is>
       </c>
-      <c r="D69" s="32" t="n">
+      <c r="D69" s="34" t="n">
         <v>177161259</v>
       </c>
-      <c r="E69" s="32" t="n">
+      <c r="E69" s="34" t="n">
         <v>183446636</v>
       </c>
-      <c r="F69" s="32" t="n">
+      <c r="F69" s="34" t="n">
         <v>191562781</v>
       </c>
-      <c r="G69" s="32" t="n">
+      <c r="G69" s="34" t="n">
         <v>196676393</v>
       </c>
       <c r="H69" s="8" t="inlineStr"/>
@@ -4986,13 +4998,13 @@
           <t>円</t>
         </is>
       </c>
-      <c r="D72" s="31" t="n">
+      <c r="D72" s="33" t="n">
         <v>107129318</v>
       </c>
-      <c r="E72" s="31" t="n">
+      <c r="E72" s="33" t="n">
         <v>118576472</v>
       </c>
-      <c r="F72" s="31" t="n">
+      <c r="F72" s="33" t="n">
         <v>118244825</v>
       </c>
       <c r="G72" s="6" t="inlineStr"/>
@@ -5013,13 +5025,13 @@
           <t>円</t>
         </is>
       </c>
-      <c r="D73" s="31" t="n">
+      <c r="D73" s="33" t="n">
         <v>70031941</v>
       </c>
-      <c r="E73" s="31" t="n">
+      <c r="E73" s="33" t="n">
         <v>72382081</v>
       </c>
-      <c r="F73" s="31" t="n">
+      <c r="F73" s="33" t="n">
         <v>70317509</v>
       </c>
       <c r="G73" s="6" t="inlineStr"/>
@@ -5040,13 +5052,13 @@
           <t>円</t>
         </is>
       </c>
-      <c r="D74" s="32" t="n">
+      <c r="D74" s="34" t="n">
         <v>177161259</v>
       </c>
-      <c r="E74" s="32" t="n">
+      <c r="E74" s="34" t="n">
         <v>190958553</v>
       </c>
-      <c r="F74" s="32" t="n">
+      <c r="F74" s="34" t="n">
         <v>188562334</v>
       </c>
       <c r="G74" s="8" t="inlineStr"/>
@@ -5396,7 +5408,7 @@
       <c r="I12" s="15" t="n">
         <v>376.2</v>
       </c>
-      <c r="J12" s="19" t="n">
+      <c r="J12" s="23" t="n">
         <v>1.116</v>
       </c>
       <c r="K12" s="6" t="inlineStr"/>
@@ -5431,7 +5443,7 @@
       <c r="I13" s="15" t="n">
         <v>159</v>
       </c>
-      <c r="J13" s="19" t="n">
+      <c r="J13" s="23" t="n">
         <v>1.112</v>
       </c>
       <c r="K13" s="6" t="inlineStr"/>
@@ -5466,7 +5478,7 @@
       <c r="I14" s="15" t="n">
         <v>3135.7</v>
       </c>
-      <c r="J14" s="19" t="n">
+      <c r="J14" s="23" t="n">
         <v>1.105</v>
       </c>
       <c r="K14" s="6" t="inlineStr"/>
@@ -5478,28 +5490,28 @@
           <t>計（延べ）</t>
         </is>
       </c>
-      <c r="C15" s="20" t="n">
+      <c r="C15" s="24" t="n">
         <v>3316.8</v>
       </c>
-      <c r="D15" s="20" t="n">
+      <c r="D15" s="24" t="n">
         <v>3458.3</v>
       </c>
-      <c r="E15" s="20" t="n">
+      <c r="E15" s="24" t="n">
         <v>3484.5</v>
       </c>
-      <c r="F15" s="20" t="n">
+      <c r="F15" s="24" t="n">
         <v>3741.8</v>
       </c>
-      <c r="G15" s="20" t="n">
+      <c r="G15" s="24" t="n">
         <v>3847.9</v>
       </c>
-      <c r="H15" s="20" t="n">
+      <c r="H15" s="24" t="n">
         <v>3686.6</v>
       </c>
-      <c r="I15" s="20" t="n">
+      <c r="I15" s="24" t="n">
         <v>3670.9</v>
       </c>
-      <c r="J15" s="21" t="n">
+      <c r="J15" s="25" t="n">
         <v>1.107</v>
       </c>
       <c r="K15" s="11" t="inlineStr"/>
@@ -5599,7 +5611,7 @@
           <t>3,245,610,859</t>
         </is>
       </c>
-      <c r="J18" s="19" t="n">
+      <c r="J18" s="23" t="n">
         <v>1.113</v>
       </c>
       <c r="K18" s="6" t="inlineStr">
@@ -5667,7 +5679,7 @@
       <c r="D22" s="5" t="n">
         <v>9213</v>
       </c>
-      <c r="E22" s="25" t="n">
+      <c r="E22" s="27" t="n">
         <v>6481</v>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -5700,7 +5712,7 @@
       <c r="D23" s="5" t="n">
         <v>9211</v>
       </c>
-      <c r="E23" s="25" t="n">
+      <c r="E23" s="27" t="n">
         <v>6530</v>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -5733,7 +5745,7 @@
       <c r="D24" s="5" t="n">
         <v>9250</v>
       </c>
-      <c r="E24" s="25" t="n">
+      <c r="E24" s="27" t="n">
         <v>7003</v>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -5766,7 +5778,7 @@
       <c r="D25" s="5" t="n">
         <v>9491</v>
       </c>
-      <c r="E25" s="25" t="n">
+      <c r="E25" s="27" t="n">
         <v>7022</v>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -5799,7 +5811,7 @@
       <c r="D26" s="5" t="n">
         <v>9395</v>
       </c>
-      <c r="E26" s="25" t="n">
+      <c r="E26" s="27" t="n">
         <v>6792</v>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -5832,7 +5844,7 @@
       <c r="D27" s="5" t="n">
         <v>9127</v>
       </c>
-      <c r="E27" s="25" t="n">
+      <c r="E27" s="27" t="n">
         <v>6951</v>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -6823,7 +6835,7 @@
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="33" t="n">
+      <c r="A6" s="35" t="n">
         <v>1</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -6846,10 +6858,10 @@
           <t>3,044,598,937</t>
         </is>
       </c>
-      <c r="F6" s="33" t="n">
+      <c r="F6" s="35" t="n">
         <v>9035.1</v>
       </c>
-      <c r="G6" s="33" t="n">
+      <c r="G6" s="35" t="n">
         <v>6438</v>
       </c>
       <c r="H6" s="9" t="inlineStr">
@@ -7025,7 +7037,7 @@
       <c r="C14" s="5" t="n">
         <v>9035.1</v>
       </c>
-      <c r="D14" s="25" t="n">
+      <c r="D14" s="27" t="n">
         <v>6438</v>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -7123,7 +7135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -7996,10 +8008,142 @@
         </is>
       </c>
     </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>住民基本台帳の趨勢の期間による差（人口の伸び率の感応度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="4" t="inlineStr"/>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>趨勢の期間</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>65〜74歳</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>75〜84歳</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>85歳以上</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>第1号計</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>算定上の月額／保険料基準額</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>6年（平成31年→令和7年）（採用）</t>
+        </is>
+      </c>
+      <c r="C33" s="37" t="n">
+        <v>3372</v>
+      </c>
+      <c r="D33" s="37" t="n">
+        <v>3689</v>
+      </c>
+      <c r="E33" s="37" t="n">
+        <v>2152</v>
+      </c>
+      <c r="F33" s="37" t="n">
+        <v>9213</v>
+      </c>
+      <c r="G33" s="20" t="inlineStr">
+        <is>
+          <t>6438.26円／6,400円</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>5年（令和2年→令和7年）</t>
+        </is>
+      </c>
+      <c r="C34" s="33" t="n">
+        <v>3316</v>
+      </c>
+      <c r="D34" s="33" t="n">
+        <v>3739</v>
+      </c>
+      <c r="E34" s="33" t="n">
+        <v>2142</v>
+      </c>
+      <c r="F34" s="33" t="n">
+        <v>9197</v>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>6444.68円／6,400円</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>3年（令和4年→令和7年）</t>
+        </is>
+      </c>
+      <c r="C35" s="33" t="n">
+        <v>3150</v>
+      </c>
+      <c r="D35" s="33" t="n">
+        <v>3999</v>
+      </c>
+      <c r="E35" s="33" t="n">
+        <v>2051</v>
+      </c>
+      <c r="F35" s="33" t="n">
+        <v>9201</v>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>6387.65円／6,400円</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="76" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>注1）いずれも令和11年度の値です。案Cの作り方（実績の水準×階級別の年平均変化率、令和12年度以降は社人研推計の伸び率で接続）は変えず、住民基本台帳の変化率を求める期間だけを変えたものです。
+注2）第1号被保険者数の計は9,197人から9,213人までの幅に収まりますが、85歳以上は2,051人から2,152人まで開きます。認定率が最も高い階級であるため、人口の計だけでは人口の置き方の妥当性を確かめられません。
+注3）算定上の月額は6387.65円から6444.68円であり、保険料基準額（百円未満四捨五入）はいずれも6,400円です。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A31:G31"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A29:G29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8012,7 +8156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -8082,7 +8226,7 @@
           <t>不一致0件</t>
         </is>
       </c>
-      <c r="E5" s="24" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -8107,7 +8251,7 @@
           <t>不一致0件</t>
         </is>
       </c>
-      <c r="E6" s="24" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -8132,7 +8276,7 @@
           <t>最大差 0.000000人</t>
         </is>
       </c>
-      <c r="E7" s="24" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -8157,7 +8301,7 @@
           <t>最大差 0.000000人</t>
         </is>
       </c>
-      <c r="E8" s="24" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -8182,7 +8326,7 @@
           <t>差 0.0028円</t>
         </is>
       </c>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -8207,7 +8351,7 @@
           <t>最大差 0.00000000</t>
         </is>
       </c>
-      <c r="E10" s="24" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -8232,7 +8376,7 @@
           <t>負の値0件</t>
         </is>
       </c>
-      <c r="E11" s="24" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -8257,7 +8401,7 @@
           <t>最大差 0.0000000000人</t>
         </is>
       </c>
-      <c r="E12" s="24" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -8282,7 +8426,7 @@
           <t>差 0.000000円</t>
         </is>
       </c>
-      <c r="E13" s="24" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -8307,7 +8451,7 @@
           <t>0でないもの0件</t>
         </is>
       </c>
-      <c r="E14" s="24" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -8332,7 +8476,7 @@
           <t>最大差 0.000000人</t>
         </is>
       </c>
-      <c r="E15" s="24" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -8357,7 +8501,7 @@
           <t>差 0.000000円</t>
         </is>
       </c>
-      <c r="E16" s="24" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -8382,7 +8526,7 @@
           <t>未記載0件</t>
         </is>
       </c>
-      <c r="E17" s="24" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -8407,7 +8551,7 @@
           <t>欠測なし</t>
         </is>
       </c>
-      <c r="E18" s="24" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -8432,7 +8576,7 @@
           <t>6427.9円（公表値6428円）</t>
         </is>
       </c>
-      <c r="E19" s="24" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -8457,7 +8601,7 @@
           <t>差 0.0000円</t>
         </is>
       </c>
-      <c r="E20" s="24" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -8482,7 +8626,7 @@
           <t>実績0 6種別。両者は同じ</t>
         </is>
       </c>
-      <c r="E21" s="24" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -8507,7 +8651,7 @@
           <t>当方の在宅の認定者数 1503.8人（差 0.1％）</t>
         </is>
       </c>
-      <c r="E22" s="24" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -8532,7 +8676,7 @@
           <t>総括表の第1号被保険者数 9,119人（差 0.05％）</t>
         </is>
       </c>
-      <c r="E23" s="24" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -8557,7 +8701,7 @@
           <t>超過 0.0／0.0／0.0人</t>
         </is>
       </c>
-      <c r="E24" s="24" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -8582,7 +8726,7 @@
           <t>同分析の＋61円と一致</t>
         </is>
       </c>
-      <c r="E25" s="24" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -8607,147 +8751,247 @@
           <t>固定値を書き写していない</t>
         </is>
       </c>
-      <c r="E26" s="24" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="11" t="inlineStr"/>
-      <c r="B27" s="11" t="inlineStr">
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>認定率シナリオ2による給付費が採用値と一致すること</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>差 0.000000円</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>円未満で一致</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>要介護度別の単価による差（単価ミックス効果）が0でないこと</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>月額 +2.16円</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>重度化により単価の平均が上がる</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>採用する認定率シナリオが将来推計 第3段階と一致すること</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>本表 2／第3段階 2</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>同じシナリオによる</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>趨勢の期間の感応度が採用値（6年）を再現すること</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>差 0.000000円</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>円未満で一致</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="11" t="inlineStr"/>
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>22件</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>適合22件・不適合0件</t>
-        </is>
-      </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>26件</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>適合26件・不適合0件</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>点検の対象としていないもの</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="32" customHeight="1">
-      <c r="A30" s="4" t="inlineStr"/>
-      <c r="B30" s="4" t="inlineStr">
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="4" t="inlineStr"/>
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>理由</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr"/>
-      <c r="E30" s="4" t="inlineStr"/>
-    </row>
-    <row r="31" ht="44" customHeight="1">
-      <c r="A31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>見込量の水準そのもの</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>対計画比は第7期からの8年度すべてで100％未満であり、計画が実績を上回る側に偏っています。本表は補正を行っていないため同じ偏りを持ち得ます（確認事項No.106）</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-    </row>
-    <row r="32" ht="44" customHeight="1">
-      <c r="A32" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>給付費データの給付費総額と年報の給付費の範囲の違い</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>給付費総額は保険請求額と保険利用者負担額の合計であり費用額に当たります。本表は年報及び総括表（保険給付費）によります</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-    </row>
-    <row r="33" ht="44" customHeight="1">
-      <c r="A33" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>報酬改定率</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>未公表であるため単価を令和7年度で固定しました（確認事項No.110）</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-    </row>
-    <row r="34" ht="44" customHeight="1">
-      <c r="A34" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>必要利用定員総数の水準</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>3町の整備方針が確定していないため、据え置き案を掲げるにとどめています</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr"/>
-      <c r="E34" s="6" t="inlineStr"/>
+      <c r="D34" s="4" t="inlineStr"/>
+      <c r="E34" s="4" t="inlineStr"/>
     </row>
     <row r="35" ht="44" customHeight="1">
       <c r="A35" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>総合事業の量の令和7年度実績</t>
+          <t>見込量の水準そのもの</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>未受領です。令和6年度の実施状況調査を据え置いています（確認事項No.112）</t>
+          <t>対計画比は第7期からの8年度すべてで100％未満であり、計画が実績を上回る側に偏っています。本表は補正を行っていないため同じ偏りを持ち得ます（確認事項No.106）</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr"/>
       <c r="E35" s="6" t="inlineStr"/>
+    </row>
+    <row r="36" ht="44" customHeight="1">
+      <c r="A36" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>給付費データの給付費総額と年報の給付費の範囲の違い</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>給付費総額は保険請求額と保険利用者負担額の合計であり費用額に当たります。本表は年報及び総括表（保険給付費）によります</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr"/>
+      <c r="E36" s="6" t="inlineStr"/>
+    </row>
+    <row r="37" ht="44" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>報酬改定率</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>未公表であるため単価を令和7年度で固定しました（確認事項No.110）</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr"/>
+      <c r="E37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="44" customHeight="1">
+      <c r="A38" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>必要利用定員総数の水準</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>3町の整備方針が確定していないため、据え置き案を掲げるにとどめています</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr"/>
+      <c r="E38" s="6" t="inlineStr"/>
+    </row>
+    <row r="39" ht="44" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>総合事業の量の令和7年度実績</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>未受領です。令和6年度の実施状況調査を据え置いています（確認事項No.112）</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr"/>
+      <c r="E39" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A29:E29"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A33:E33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8759,7 +9003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -8910,7 +9154,7 @@
       <c r="A9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="28" t="inlineStr">
         <is>
           <t>ご確認</t>
         </is>
@@ -8935,7 +9179,7 @@
       <c r="A10" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>ご確認</t>
         </is>
@@ -8960,7 +9204,7 @@
       <c r="A11" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="27" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>ご依頼</t>
         </is>
@@ -8985,7 +9229,7 @@
       <c r="A12" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>ご確認</t>
         </is>
@@ -9022,7 +9266,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>総括表詳細（４）は要介護度別の内訳を持たないため、計画作成支援ツールの要介護度別の1人1月あたり給付費から要介護度間の比（形）だけを採り、水準は総括表（保険者単位）に合わせて比例調整しました。基準年度では総括表の給付費を円単位で再現します。要介護度の構成が重度側へ動く分だけ平均の単価が上がり、令和11年度＋0.047％（月額＋2円）・令和22年度＋0.280％です。ツールは3町合計であり、要介護度間の比が保険者単位でも同じであることを確かめられていません。本表の採用値は単価固定（06シート）のままとしています。</t>
+          <t>総括表詳細（４）は要介護度別の内訳を持たないため、給付費データ（保険者単位）の要介護度別の1人1月あたり給付費から要介護度間の比（形）だけを採り、水準は総括表（保険者単位）に合わせて比例調整しました。基準年度では総括表の給付費を円単位で再現します。要介護度の構成が重度側へ動く分だけ平均の単価が上がり、令和11年度+0.047％（月額+2.16円）・令和22年度+0.280％です。本表の採用値は要介護度別の単価（07シート）です。</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -9035,24 +9279,24 @@
       <c r="A14" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="26" t="inlineStr">
-        <is>
-          <t>ご協議</t>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>ご判断</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>地域密着型介護老人福祉施設入所者生活介護が令和11年度に定員に達する見込みであることへの対応</t>
+          <t>認定率の置き方（①現状固定・②トレンド継続・③令和元年水準）</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>本表の見込みでは令和11年度に61.9人／月となり、区域内の定員62人の99.9％に達する見込みです。令和12年度には超えると見込まれます。①区域外の施設の利用で受け止めるか、②整備するか、③見込量の側を定員で頭打ちにするかのご協議をお願いします。年報は施設の所在地を問わず当連合の被保険者を数えるため、区域内の定員は上限ではありません（確認事項No.141）。本表は頭打ちを課していません（第10期は差が生じません）。</t>
+          <t>本表は②トレンド継続によっています。置き方により算定上の月額基準額が①6,523円・②6,438円・③6,672円となり、百円未満を四捨五入した保険料基準額は①6,500円・②6,400円・③6,700円に分かれます。②は3つのうち最も低く出る置き方です。</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月26日まで</t>
+          <t>令和8年10月30日まで</t>
         </is>
       </c>
     </row>
@@ -9060,29 +9304,54 @@
       <c r="A15" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="28" t="inlineStr">
+        <is>
+          <t>ご協議</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型介護老人福祉施設入所者生活介護が令和11年度に定員に達する見込みであることへの対応</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>本表の見込みでは令和11年度に61.9人／月となり、区域内の定員62人の99.9％に達する見込みです。令和12年度には超えると見込まれます。①区域外の施設の利用で受け止めるか、②整備するか、③見込量の側を定員で頭打ちにするかのご協議をお願いします。年報は施設の所在地を問わず当連合の被保険者を数えるため、区域内の定員は上限ではありません（確認事項No.141）。本表は頭打ちを課していません（第10期は差が生じません）。</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>令和8年9月26日まで</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="72" customHeight="1">
+      <c r="A16" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>ご判断</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>報酬改定率と単価の趨勢のどちらによるか</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>単価は改定の有無に関係なく年率1.75％で伸びています（改定のあった年＋1.42％・なかった年＋2.20％で差が見られません）。改定率を乗じることと趨勢を延ばすことを重ねると二重になります。改定率1％あたり月額＋61円、趨勢を織り込むと月額＋245円〜＋327円です。どちらか一方によることをご判断いただく必要があります（確認事項No.110・No.137と一体）。</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>令和8年10月30日まで</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>注）確認事項は業務工程管理表 03_確認事項一覧で一元管理します。計画素案の本文には確認事項の注記を書きません。</t>
         </is>
@@ -9091,8 +9360,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A17:E17"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A18:E18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9450,7 +9719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10307,10 +10576,188 @@
         </is>
       </c>
     </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>4　認定率の置き方（シナリオ）による差</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>置き方</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>3年計</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>総給付費
+（3か年）</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>算定上の
+月額基準額</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>保険料基準額</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>① 現状固定</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>令和8年3月末の認定率をそのまま固定する</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="n">
+        <v>2044.6</v>
+      </c>
+      <c r="D38" s="15" t="n">
+        <v>2075.9</v>
+      </c>
+      <c r="E38" s="15" t="n">
+        <v>2107.8</v>
+      </c>
+      <c r="F38" s="15" t="n">
+        <v>6228.3</v>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>9,161,306,423</t>
+        </is>
+      </c>
+      <c r="H38" s="19" t="n">
+        <v>6523.24</v>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>6,500円</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="20" t="inlineStr">
+        <is>
+          <t>② トレンド継続（採用）</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>令和元年から令和8年の変化を令和11年度まで延長する</t>
+        </is>
+      </c>
+      <c r="C39" s="21" t="n">
+        <v>2025.1</v>
+      </c>
+      <c r="D39" s="21" t="n">
+        <v>2046.1</v>
+      </c>
+      <c r="E39" s="21" t="n">
+        <v>2067.4</v>
+      </c>
+      <c r="F39" s="21" t="n">
+        <v>6138.7</v>
+      </c>
+      <c r="G39" s="20" t="inlineStr">
+        <is>
+          <t>9,035,114,142</t>
+        </is>
+      </c>
+      <c r="H39" s="22" t="n">
+        <v>6438.26</v>
+      </c>
+      <c r="I39" s="20" t="inlineStr">
+        <is>
+          <t>6,400円</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>③ 令和元年水準</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>令和11年度にかけて令和元年の水準へ戻る</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="n">
+        <v>2078.8</v>
+      </c>
+      <c r="D40" s="15" t="n">
+        <v>2128</v>
+      </c>
+      <c r="E40" s="15" t="n">
+        <v>2178.4</v>
+      </c>
+      <c r="F40" s="15" t="n">
+        <v>6385.1</v>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>9,382,142,914</t>
+        </is>
+      </c>
+      <c r="H40" s="19" t="n">
+        <v>6671.97</v>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>6,700円</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="76" customHeight="1">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>注1）本表は②によっています。いずれの置き方でも認定者数は増えますが、保険料基準額は①6,500円・②6,400円・③6,700円に分かれます。②は3つのうち最も低く出る置き方であり、単価を令和7年度で固定していることなどと併せ、算定上の月額基準額は低い側の水準にあります。［要協議］
+注2）認定者数以外の前提（利用率・単価・地域支援事業費・第1号被保険者負担割合・予定収納率・基金の取崩し）は3つとも同じです。補正後被保険者数（27301.19人）も同じであり、差は給付費のみによります。
+注3）シナリオの別は年齢階級別の認定率の置き方であり、年齢階級ごとの要介護度の構成（令和7年度末で固定）は3つとも同じです。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="9">
+    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A10:I10"/>
+    <mergeCell ref="A36:I36"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A34:I34"/>
     <mergeCell ref="A12:I12"/>
@@ -10424,7 +10871,7 @@
       <c r="G5" s="15" t="n">
         <v>144.6</v>
       </c>
-      <c r="H5" s="19" t="n">
+      <c r="H5" s="23" t="n">
         <v>1.046</v>
       </c>
       <c r="I5" s="6" t="inlineStr"/>
@@ -10455,7 +10902,7 @@
       <c r="G6" s="15" t="n">
         <v>61.9</v>
       </c>
-      <c r="H6" s="19" t="n">
+      <c r="H6" s="23" t="n">
         <v>1.045</v>
       </c>
       <c r="I6" s="6" t="inlineStr"/>
@@ -10486,7 +10933,7 @@
       <c r="G7" s="15" t="n">
         <v>140.1</v>
       </c>
-      <c r="H7" s="19" t="n">
+      <c r="H7" s="23" t="n">
         <v>1.045</v>
       </c>
       <c r="I7" s="6" t="inlineStr"/>
@@ -10517,7 +10964,7 @@
       <c r="G8" s="15" t="n">
         <v>5.7</v>
       </c>
-      <c r="H8" s="19" t="n">
+      <c r="H8" s="23" t="n">
         <v>1.041</v>
       </c>
       <c r="I8" s="6" t="inlineStr"/>
@@ -10585,7 +11032,7 @@
       <c r="G10" s="15" t="n">
         <v>64.09999999999999</v>
       </c>
-      <c r="H10" s="19" t="n">
+      <c r="H10" s="23" t="n">
         <v>1.043</v>
       </c>
       <c r="I10" s="6" t="inlineStr"/>
@@ -10653,7 +11100,7 @@
       <c r="G12" s="15" t="n">
         <v>85.2</v>
       </c>
-      <c r="H12" s="19" t="n">
+      <c r="H12" s="23" t="n">
         <v>1.045</v>
       </c>
       <c r="I12" s="6" t="inlineStr"/>
@@ -10684,7 +11131,7 @@
       <c r="G13" s="15" t="n">
         <v>281.8</v>
       </c>
-      <c r="H13" s="19" t="n">
+      <c r="H13" s="23" t="n">
         <v>1.043</v>
       </c>
       <c r="I13" s="6" t="inlineStr"/>
@@ -10715,7 +11162,7 @@
       <c r="G14" s="15" t="n">
         <v>5.5</v>
       </c>
-      <c r="H14" s="19" t="n">
+      <c r="H14" s="23" t="n">
         <v>1.042</v>
       </c>
       <c r="I14" s="6" t="inlineStr"/>
@@ -10746,7 +11193,7 @@
       <c r="G15" s="15" t="n">
         <v>140.9</v>
       </c>
-      <c r="H15" s="19" t="n">
+      <c r="H15" s="23" t="n">
         <v>1.042</v>
       </c>
       <c r="I15" s="6" t="inlineStr"/>
@@ -10777,7 +11224,7 @@
       <c r="G16" s="15" t="n">
         <v>69.8</v>
       </c>
-      <c r="H16" s="19" t="n">
+      <c r="H16" s="23" t="n">
         <v>1.042</v>
       </c>
       <c r="I16" s="6" t="inlineStr"/>
@@ -10808,7 +11255,7 @@
       <c r="G17" s="15" t="n">
         <v>201.7</v>
       </c>
-      <c r="H17" s="19" t="n">
+      <c r="H17" s="23" t="n">
         <v>1.044</v>
       </c>
       <c r="I17" s="6" t="inlineStr"/>
@@ -10839,7 +11286,7 @@
       <c r="G18" s="15" t="n">
         <v>101.5</v>
       </c>
-      <c r="H18" s="19" t="n">
+      <c r="H18" s="23" t="n">
         <v>1.043</v>
       </c>
       <c r="I18" s="6" t="inlineStr"/>
@@ -10870,7 +11317,7 @@
       <c r="G19" s="15" t="n">
         <v>79.40000000000001</v>
       </c>
-      <c r="H19" s="19" t="n">
+      <c r="H19" s="23" t="n">
         <v>1.043</v>
       </c>
       <c r="I19" s="6" t="inlineStr"/>
@@ -10901,7 +11348,7 @@
       <c r="G20" s="15" t="n">
         <v>284.6</v>
       </c>
-      <c r="H20" s="19" t="n">
+      <c r="H20" s="23" t="n">
         <v>1.042</v>
       </c>
       <c r="I20" s="6" t="inlineStr"/>
@@ -10932,7 +11379,7 @@
       <c r="G21" s="15" t="n">
         <v>27.7</v>
       </c>
-      <c r="H21" s="19" t="n">
+      <c r="H21" s="23" t="n">
         <v>1.044</v>
       </c>
       <c r="I21" s="6" t="inlineStr"/>
@@ -10963,7 +11410,7 @@
       <c r="G22" s="15" t="n">
         <v>17.3</v>
       </c>
-      <c r="H22" s="19" t="n">
+      <c r="H22" s="23" t="n">
         <v>1.045</v>
       </c>
       <c r="I22" s="6" t="inlineStr"/>
@@ -11068,7 +11515,7 @@
       <c r="G25" s="15" t="n">
         <v>669.1</v>
       </c>
-      <c r="H25" s="19" t="n">
+      <c r="H25" s="23" t="n">
         <v>1.042</v>
       </c>
       <c r="I25" s="6" t="inlineStr"/>
@@ -11099,7 +11546,7 @@
       <c r="G26" s="15" t="n">
         <v>11.2</v>
       </c>
-      <c r="H26" s="19" t="n">
+      <c r="H26" s="23" t="n">
         <v>1.041</v>
       </c>
       <c r="I26" s="6" t="inlineStr"/>
@@ -11130,7 +11577,7 @@
       <c r="G27" s="15" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="H27" s="19" t="n">
+      <c r="H27" s="23" t="n">
         <v>1.041</v>
       </c>
       <c r="I27" s="6" t="inlineStr"/>
@@ -11161,7 +11608,7 @@
       <c r="G28" s="15" t="n">
         <v>0.6</v>
       </c>
-      <c r="H28" s="19" t="n">
+      <c r="H28" s="23" t="n">
         <v>1.04</v>
       </c>
       <c r="I28" s="6" t="inlineStr"/>
@@ -11229,7 +11676,7 @@
       <c r="G30" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="H30" s="19" t="n">
+      <c r="H30" s="23" t="n">
         <v>1.045</v>
       </c>
       <c r="I30" s="6" t="inlineStr"/>
@@ -11260,7 +11707,7 @@
       <c r="G31" s="15" t="n">
         <v>104.2</v>
       </c>
-      <c r="H31" s="19" t="n">
+      <c r="H31" s="23" t="n">
         <v>1.043</v>
       </c>
       <c r="I31" s="6" t="inlineStr"/>
@@ -11328,7 +11775,7 @@
       <c r="G33" s="15" t="n">
         <v>951.5</v>
       </c>
-      <c r="H33" s="19" t="n">
+      <c r="H33" s="23" t="n">
         <v>1.042</v>
       </c>
       <c r="I33" s="6" t="inlineStr"/>
@@ -11345,19 +11792,19 @@
           <t>（延べ）</t>
         </is>
       </c>
-      <c r="D34" s="20" t="n">
+      <c r="D34" s="24" t="n">
         <v>3316.8</v>
       </c>
-      <c r="E34" s="20" t="n">
+      <c r="E34" s="24" t="n">
         <v>3386.5</v>
       </c>
-      <c r="F34" s="20" t="n">
+      <c r="F34" s="24" t="n">
         <v>3422.1</v>
       </c>
-      <c r="G34" s="20" t="n">
+      <c r="G34" s="24" t="n">
         <v>3458.3</v>
       </c>
-      <c r="H34" s="21" t="n">
+      <c r="H34" s="25" t="n">
         <v>1.043</v>
       </c>
       <c r="I34" s="11" t="inlineStr">
@@ -11430,7 +11877,7 @@
       <c r="G38" s="15" t="n">
         <v>352.3</v>
       </c>
-      <c r="H38" s="19" t="n">
+      <c r="H38" s="23" t="n">
         <v>1.045</v>
       </c>
       <c r="I38" s="6" t="inlineStr"/>
@@ -11457,7 +11904,7 @@
       <c r="G39" s="15" t="n">
         <v>149.4</v>
       </c>
-      <c r="H39" s="19" t="n">
+      <c r="H39" s="23" t="n">
         <v>1.044</v>
       </c>
       <c r="I39" s="6" t="inlineStr"/>
@@ -11484,7 +11931,7 @@
       <c r="G40" s="15" t="n">
         <v>2956.6</v>
       </c>
-      <c r="H40" s="19" t="n">
+      <c r="H40" s="23" t="n">
         <v>1.042</v>
       </c>
       <c r="I40" s="6" t="inlineStr"/>
@@ -11608,28 +12055,28 @@
           <t>介護老人福祉施設</t>
         </is>
       </c>
-      <c r="C6" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="22" t="n">
+      <c r="C6" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="19" t="n">
         <v>5.75</v>
       </c>
-      <c r="F6" s="22" t="n">
+      <c r="F6" s="19" t="n">
         <v>18.33</v>
       </c>
-      <c r="G6" s="22" t="n">
+      <c r="G6" s="19" t="n">
         <v>43</v>
       </c>
-      <c r="H6" s="22" t="n">
+      <c r="H6" s="19" t="n">
         <v>46.33</v>
       </c>
-      <c r="I6" s="22" t="n">
+      <c r="I6" s="19" t="n">
         <v>24.83</v>
       </c>
-      <c r="J6" s="22" t="n">
+      <c r="J6" s="19" t="n">
         <v>138.25</v>
       </c>
     </row>
@@ -11642,28 +12089,28 @@
           <t>地域密着型介護老人福祉施設入所者生活介護</t>
         </is>
       </c>
-      <c r="C7" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="22" t="n">
+      <c r="C7" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="19" t="n">
         <v>2.17</v>
       </c>
-      <c r="F7" s="22" t="n">
+      <c r="F7" s="19" t="n">
         <v>10.67</v>
       </c>
-      <c r="G7" s="22" t="n">
+      <c r="G7" s="19" t="n">
         <v>10.17</v>
       </c>
-      <c r="H7" s="22" t="n">
+      <c r="H7" s="19" t="n">
         <v>21.42</v>
       </c>
-      <c r="I7" s="22" t="n">
+      <c r="I7" s="19" t="n">
         <v>14.83</v>
       </c>
-      <c r="J7" s="22" t="n">
+      <c r="J7" s="19" t="n">
         <v>59.25</v>
       </c>
     </row>
@@ -11676,28 +12123,28 @@
           <t>介護老人保健施設</t>
         </is>
       </c>
-      <c r="C8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="22" t="n">
+      <c r="C8" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="19" t="n">
         <v>30.5</v>
       </c>
-      <c r="F8" s="22" t="n">
+      <c r="F8" s="19" t="n">
         <v>30.92</v>
       </c>
-      <c r="G8" s="22" t="n">
+      <c r="G8" s="19" t="n">
         <v>25.5</v>
       </c>
-      <c r="H8" s="22" t="n">
+      <c r="H8" s="19" t="n">
         <v>33.17</v>
       </c>
-      <c r="I8" s="22" t="n">
+      <c r="I8" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="J8" s="22" t="n">
+      <c r="J8" s="19" t="n">
         <v>134.08</v>
       </c>
     </row>
@@ -11710,28 +12157,28 @@
           <t>介護医療院</t>
         </is>
       </c>
-      <c r="C9" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="22" t="n">
+      <c r="C9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="19" t="n">
         <v>0.08</v>
       </c>
-      <c r="I9" s="22" t="n">
+      <c r="I9" s="19" t="n">
         <v>5.42</v>
       </c>
-      <c r="J9" s="22" t="n">
+      <c r="J9" s="19" t="n">
         <v>5.5</v>
       </c>
     </row>
@@ -11744,28 +12191,28 @@
           <t>介護療養型医療施設</t>
         </is>
       </c>
-      <c r="C10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="22" t="n">
+      <c r="C10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11778,28 +12225,28 @@
           <t>特定施設入居者生活介護</t>
         </is>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="D11" s="22" t="n">
+      <c r="D11" s="19" t="n">
         <v>5.33</v>
       </c>
-      <c r="E11" s="22" t="n">
+      <c r="E11" s="19" t="n">
         <v>14.92</v>
       </c>
-      <c r="F11" s="22" t="n">
+      <c r="F11" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="G11" s="22" t="n">
+      <c r="G11" s="19" t="n">
         <v>8.17</v>
       </c>
-      <c r="H11" s="22" t="n">
+      <c r="H11" s="19" t="n">
         <v>10.75</v>
       </c>
-      <c r="I11" s="22" t="n">
+      <c r="I11" s="19" t="n">
         <v>6.33</v>
       </c>
-      <c r="J11" s="22" t="n">
+      <c r="J11" s="19" t="n">
         <v>61.5</v>
       </c>
     </row>
@@ -11812,28 +12259,28 @@
           <t>地域密着型特定施設入居者生活介護</t>
         </is>
       </c>
-      <c r="C12" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="22" t="n">
+      <c r="C12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11846,28 +12293,28 @@
           <t>認知症対応型共同生活介護</t>
         </is>
       </c>
-      <c r="C13" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="22" t="n">
+      <c r="C13" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="19" t="n">
         <v>0.42</v>
       </c>
-      <c r="E13" s="22" t="n">
+      <c r="E13" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="F13" s="22" t="n">
+      <c r="F13" s="19" t="n">
         <v>18.67</v>
       </c>
-      <c r="G13" s="22" t="n">
+      <c r="G13" s="19" t="n">
         <v>21.75</v>
       </c>
-      <c r="H13" s="22" t="n">
+      <c r="H13" s="19" t="n">
         <v>15</v>
       </c>
-      <c r="I13" s="22" t="n">
+      <c r="I13" s="19" t="n">
         <v>13.75</v>
       </c>
-      <c r="J13" s="22" t="n">
+      <c r="J13" s="19" t="n">
         <v>81.58</v>
       </c>
     </row>
@@ -11880,28 +12327,28 @@
           <t>訪問介護</t>
         </is>
       </c>
-      <c r="C14" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="22" t="n">
+      <c r="C14" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="19" t="n">
         <v>99.92</v>
       </c>
-      <c r="F14" s="22" t="n">
+      <c r="F14" s="19" t="n">
         <v>49.67</v>
       </c>
-      <c r="G14" s="22" t="n">
+      <c r="G14" s="19" t="n">
         <v>42.58</v>
       </c>
-      <c r="H14" s="22" t="n">
+      <c r="H14" s="19" t="n">
         <v>44.42</v>
       </c>
-      <c r="I14" s="22" t="n">
+      <c r="I14" s="19" t="n">
         <v>33.5</v>
       </c>
-      <c r="J14" s="22" t="n">
+      <c r="J14" s="19" t="n">
         <v>270.08</v>
       </c>
     </row>
@@ -11914,28 +12361,28 @@
           <t>訪問入浴介護</t>
         </is>
       </c>
-      <c r="C15" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="22" t="n">
+      <c r="C15" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="19" t="n">
         <v>1.17</v>
       </c>
-      <c r="F15" s="22" t="n">
+      <c r="F15" s="19" t="n">
         <v>0.25</v>
       </c>
-      <c r="G15" s="22" t="n">
+      <c r="G15" s="19" t="n">
         <v>0.25</v>
       </c>
-      <c r="H15" s="22" t="n">
+      <c r="H15" s="19" t="n">
         <v>1.17</v>
       </c>
-      <c r="I15" s="22" t="n">
+      <c r="I15" s="19" t="n">
         <v>2.42</v>
       </c>
-      <c r="J15" s="22" t="n">
+      <c r="J15" s="19" t="n">
         <v>5.25</v>
       </c>
     </row>
@@ -11948,28 +12395,28 @@
           <t>訪問看護</t>
         </is>
       </c>
-      <c r="C16" s="22" t="n">
+      <c r="C16" s="19" t="n">
         <v>10.25</v>
       </c>
-      <c r="D16" s="22" t="n">
+      <c r="D16" s="19" t="n">
         <v>14.17</v>
       </c>
-      <c r="E16" s="22" t="n">
+      <c r="E16" s="19" t="n">
         <v>41.08</v>
       </c>
-      <c r="F16" s="22" t="n">
+      <c r="F16" s="19" t="n">
         <v>25.42</v>
       </c>
-      <c r="G16" s="22" t="n">
+      <c r="G16" s="19" t="n">
         <v>13.83</v>
       </c>
-      <c r="H16" s="22" t="n">
+      <c r="H16" s="19" t="n">
         <v>15.17</v>
       </c>
-      <c r="I16" s="22" t="n">
+      <c r="I16" s="19" t="n">
         <v>15.25</v>
       </c>
-      <c r="J16" s="22" t="n">
+      <c r="J16" s="19" t="n">
         <v>135.17</v>
       </c>
     </row>
@@ -11982,28 +12429,28 @@
           <t>訪問リハビリテーション</t>
         </is>
       </c>
-      <c r="C17" s="22" t="n">
+      <c r="C17" s="19" t="n">
         <v>3.17</v>
       </c>
-      <c r="D17" s="22" t="n">
+      <c r="D17" s="19" t="n">
         <v>10.33</v>
       </c>
-      <c r="E17" s="22" t="n">
+      <c r="E17" s="19" t="n">
         <v>20.25</v>
       </c>
-      <c r="F17" s="22" t="n">
+      <c r="F17" s="19" t="n">
         <v>16.83</v>
       </c>
-      <c r="G17" s="22" t="n">
+      <c r="G17" s="19" t="n">
         <v>7.83</v>
       </c>
-      <c r="H17" s="22" t="n">
+      <c r="H17" s="19" t="n">
         <v>3.83</v>
       </c>
-      <c r="I17" s="22" t="n">
+      <c r="I17" s="19" t="n">
         <v>4.67</v>
       </c>
-      <c r="J17" s="22" t="n">
+      <c r="J17" s="19" t="n">
         <v>66.92</v>
       </c>
     </row>
@@ -12016,28 +12463,28 @@
           <t>居宅療養管理指導</t>
         </is>
       </c>
-      <c r="C18" s="22" t="n">
+      <c r="C18" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="D18" s="22" t="n">
+      <c r="D18" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="E18" s="22" t="n">
+      <c r="E18" s="19" t="n">
         <v>37.5</v>
       </c>
-      <c r="F18" s="22" t="n">
+      <c r="F18" s="19" t="n">
         <v>31.08</v>
       </c>
-      <c r="G18" s="22" t="n">
+      <c r="G18" s="19" t="n">
         <v>37.5</v>
       </c>
-      <c r="H18" s="22" t="n">
+      <c r="H18" s="19" t="n">
         <v>39.83</v>
       </c>
-      <c r="I18" s="22" t="n">
+      <c r="I18" s="19" t="n">
         <v>33.33</v>
       </c>
-      <c r="J18" s="22" t="n">
+      <c r="J18" s="19" t="n">
         <v>193.25</v>
       </c>
     </row>
@@ -12050,28 +12497,28 @@
           <t>通所介護</t>
         </is>
       </c>
-      <c r="C19" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="22" t="n">
+      <c r="C19" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="19" t="n">
         <v>49.67</v>
       </c>
-      <c r="F19" s="22" t="n">
+      <c r="F19" s="19" t="n">
         <v>22.08</v>
       </c>
-      <c r="G19" s="22" t="n">
+      <c r="G19" s="19" t="n">
         <v>10.75</v>
       </c>
-      <c r="H19" s="22" t="n">
+      <c r="H19" s="19" t="n">
         <v>11.67</v>
       </c>
-      <c r="I19" s="22" t="n">
+      <c r="I19" s="19" t="n">
         <v>3.17</v>
       </c>
-      <c r="J19" s="22" t="n">
+      <c r="J19" s="19" t="n">
         <v>97.33</v>
       </c>
     </row>
@@ -12084,28 +12531,28 @@
           <t>地域密着型通所介護</t>
         </is>
       </c>
-      <c r="C20" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="22" t="n">
+      <c r="C20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="19" t="n">
         <v>37.08</v>
       </c>
-      <c r="F20" s="22" t="n">
+      <c r="F20" s="19" t="n">
         <v>23.58</v>
       </c>
-      <c r="G20" s="22" t="n">
+      <c r="G20" s="19" t="n">
         <v>8.67</v>
       </c>
-      <c r="H20" s="22" t="n">
+      <c r="H20" s="19" t="n">
         <v>3.83</v>
       </c>
-      <c r="I20" s="22" t="n">
+      <c r="I20" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J20" s="22" t="n">
+      <c r="J20" s="19" t="n">
         <v>76.17</v>
       </c>
     </row>
@@ -12118,28 +12565,28 @@
           <t>通所リハビリテーション</t>
         </is>
       </c>
-      <c r="C21" s="22" t="n">
+      <c r="C21" s="19" t="n">
         <v>31.17</v>
       </c>
-      <c r="D21" s="22" t="n">
+      <c r="D21" s="19" t="n">
         <v>52.25</v>
       </c>
-      <c r="E21" s="22" t="n">
+      <c r="E21" s="19" t="n">
         <v>97.75</v>
       </c>
-      <c r="F21" s="22" t="n">
+      <c r="F21" s="19" t="n">
         <v>51.92</v>
       </c>
-      <c r="G21" s="22" t="n">
+      <c r="G21" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="H21" s="22" t="n">
+      <c r="H21" s="19" t="n">
         <v>13.5</v>
       </c>
-      <c r="I21" s="22" t="n">
+      <c r="I21" s="19" t="n">
         <v>6.67</v>
       </c>
-      <c r="J21" s="22" t="n">
+      <c r="J21" s="19" t="n">
         <v>273.25</v>
       </c>
     </row>
@@ -12152,28 +12599,28 @@
           <t>短期入所生活介護</t>
         </is>
       </c>
-      <c r="C22" s="22" t="n">
+      <c r="C22" s="19" t="n">
         <v>0.58</v>
       </c>
-      <c r="D22" s="22" t="n">
+      <c r="D22" s="19" t="n">
         <v>0.92</v>
       </c>
-      <c r="E22" s="22" t="n">
+      <c r="E22" s="19" t="n">
         <v>6.42</v>
       </c>
-      <c r="F22" s="22" t="n">
+      <c r="F22" s="19" t="n">
         <v>10.42</v>
       </c>
-      <c r="G22" s="22" t="n">
+      <c r="G22" s="19" t="n">
         <v>3.42</v>
       </c>
-      <c r="H22" s="22" t="n">
+      <c r="H22" s="19" t="n">
         <v>3.5</v>
       </c>
-      <c r="I22" s="22" t="n">
+      <c r="I22" s="19" t="n">
         <v>1.25</v>
       </c>
-      <c r="J22" s="22" t="n">
+      <c r="J22" s="19" t="n">
         <v>26.5</v>
       </c>
     </row>
@@ -12186,28 +12633,28 @@
           <t>短期入所療養介護（老健）</t>
         </is>
       </c>
-      <c r="C23" s="22" t="n">
+      <c r="C23" s="19" t="n">
         <v>0.42</v>
       </c>
-      <c r="D23" s="22" t="n">
+      <c r="D23" s="19" t="n">
         <v>0.08</v>
       </c>
-      <c r="E23" s="22" t="n">
+      <c r="E23" s="19" t="n">
         <v>2.83</v>
       </c>
-      <c r="F23" s="22" t="n">
+      <c r="F23" s="19" t="n">
         <v>5.17</v>
       </c>
-      <c r="G23" s="22" t="n">
+      <c r="G23" s="19" t="n">
         <v>2.75</v>
       </c>
-      <c r="H23" s="22" t="n">
+      <c r="H23" s="19" t="n">
         <v>4.17</v>
       </c>
-      <c r="I23" s="22" t="n">
+      <c r="I23" s="19" t="n">
         <v>1.17</v>
       </c>
-      <c r="J23" s="22" t="n">
+      <c r="J23" s="19" t="n">
         <v>16.58</v>
       </c>
     </row>
@@ -12220,28 +12667,28 @@
           <t>短期入所療養介護（病院等）</t>
         </is>
       </c>
-      <c r="C24" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="22" t="n">
+      <c r="C24" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12254,28 +12701,28 @@
           <t>短期入所療養介護（介護医療院）</t>
         </is>
       </c>
-      <c r="C25" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="22" t="n">
+      <c r="C25" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12288,28 +12735,28 @@
           <t>福祉用具貸与</t>
         </is>
       </c>
-      <c r="C26" s="22" t="n">
+      <c r="C26" s="19" t="n">
         <v>66.25</v>
       </c>
-      <c r="D26" s="22" t="n">
+      <c r="D26" s="19" t="n">
         <v>118.75</v>
       </c>
-      <c r="E26" s="22" t="n">
+      <c r="E26" s="19" t="n">
         <v>177.5</v>
       </c>
-      <c r="F26" s="22" t="n">
+      <c r="F26" s="19" t="n">
         <v>123</v>
       </c>
-      <c r="G26" s="22" t="n">
+      <c r="G26" s="19" t="n">
         <v>65.92</v>
       </c>
-      <c r="H26" s="22" t="n">
+      <c r="H26" s="19" t="n">
         <v>49.67</v>
       </c>
-      <c r="I26" s="22" t="n">
+      <c r="I26" s="19" t="n">
         <v>41</v>
       </c>
-      <c r="J26" s="22" t="n">
+      <c r="J26" s="19" t="n">
         <v>642.08</v>
       </c>
     </row>
@@ -12322,28 +12769,28 @@
           <t>特定福祉用具販売</t>
         </is>
       </c>
-      <c r="C27" s="22" t="n">
+      <c r="C27" s="19" t="n">
         <v>1.67</v>
       </c>
-      <c r="D27" s="22" t="n">
+      <c r="D27" s="19" t="n">
         <v>2.08</v>
       </c>
-      <c r="E27" s="22" t="n">
+      <c r="E27" s="19" t="n">
         <v>3.5</v>
       </c>
-      <c r="F27" s="22" t="n">
+      <c r="F27" s="19" t="n">
         <v>2.17</v>
       </c>
-      <c r="G27" s="22" t="n">
+      <c r="G27" s="19" t="n">
         <v>0.67</v>
       </c>
-      <c r="H27" s="22" t="n">
+      <c r="H27" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="I27" s="22" t="n">
+      <c r="I27" s="19" t="n">
         <v>0.17</v>
       </c>
-      <c r="J27" s="22" t="n">
+      <c r="J27" s="19" t="n">
         <v>10.75</v>
       </c>
     </row>
@@ -12356,28 +12803,28 @@
           <t>住宅改修</t>
         </is>
       </c>
-      <c r="C28" s="22" t="n">
+      <c r="C28" s="19" t="n">
         <v>2.25</v>
       </c>
-      <c r="D28" s="22" t="n">
+      <c r="D28" s="19" t="n">
         <v>1.58</v>
       </c>
-      <c r="E28" s="22" t="n">
+      <c r="E28" s="19" t="n">
         <v>2.33</v>
       </c>
-      <c r="F28" s="22" t="n">
+      <c r="F28" s="19" t="n">
         <v>1.25</v>
       </c>
-      <c r="G28" s="22" t="n">
+      <c r="G28" s="19" t="n">
         <v>0.58</v>
       </c>
-      <c r="H28" s="22" t="n">
+      <c r="H28" s="19" t="n">
         <v>0.17</v>
       </c>
-      <c r="I28" s="22" t="n">
+      <c r="I28" s="19" t="n">
         <v>0.25</v>
       </c>
-      <c r="J28" s="22" t="n">
+      <c r="J28" s="19" t="n">
         <v>8.42</v>
       </c>
     </row>
@@ -12390,28 +12837,28 @@
           <t>定期巡回・随時対応型訪問介護看護</t>
         </is>
       </c>
-      <c r="C29" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="22" t="n">
+      <c r="C29" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="19" t="n">
         <v>0.25</v>
       </c>
-      <c r="F29" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="22" t="n">
+      <c r="F29" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="19" t="n">
         <v>0.33</v>
       </c>
-      <c r="J29" s="22" t="n">
+      <c r="J29" s="19" t="n">
         <v>0.58</v>
       </c>
     </row>
@@ -12424,28 +12871,28 @@
           <t>夜間対応型訪問介護</t>
         </is>
       </c>
-      <c r="C30" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="22" t="n">
+      <c r="C30" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12458,28 +12905,28 @@
           <t>認知症対応型通所介護</t>
         </is>
       </c>
-      <c r="C31" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="22" t="n">
+      <c r="C31" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G31" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="22" t="n">
+      <c r="G31" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12492,28 +12939,28 @@
           <t>小規模多機能型居宅介護</t>
         </is>
       </c>
-      <c r="C32" s="22" t="n">
+      <c r="C32" s="19" t="n">
         <v>4.17</v>
       </c>
-      <c r="D32" s="22" t="n">
+      <c r="D32" s="19" t="n">
         <v>9.33</v>
       </c>
-      <c r="E32" s="22" t="n">
+      <c r="E32" s="19" t="n">
         <v>37.75</v>
       </c>
-      <c r="F32" s="22" t="n">
+      <c r="F32" s="19" t="n">
         <v>23.08</v>
       </c>
-      <c r="G32" s="22" t="n">
+      <c r="G32" s="19" t="n">
         <v>17.17</v>
       </c>
-      <c r="H32" s="22" t="n">
+      <c r="H32" s="19" t="n">
         <v>3.33</v>
       </c>
-      <c r="I32" s="22" t="n">
+      <c r="I32" s="19" t="n">
         <v>5.08</v>
       </c>
-      <c r="J32" s="22" t="n">
+      <c r="J32" s="19" t="n">
         <v>99.92</v>
       </c>
     </row>
@@ -12526,28 +12973,28 @@
           <t>看護小規模多機能型居宅介護</t>
         </is>
       </c>
-      <c r="C33" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="22" t="n">
+      <c r="C33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12560,28 +13007,28 @@
           <t>介護予防支援・居宅介護支援</t>
         </is>
       </c>
-      <c r="C34" s="22" t="n">
+      <c r="C34" s="19" t="n">
         <v>100.25</v>
       </c>
-      <c r="D34" s="22" t="n">
+      <c r="D34" s="19" t="n">
         <v>156.67</v>
       </c>
-      <c r="E34" s="22" t="n">
+      <c r="E34" s="19" t="n">
         <v>298.58</v>
       </c>
-      <c r="F34" s="22" t="n">
+      <c r="F34" s="19" t="n">
         <v>167.58</v>
       </c>
-      <c r="G34" s="22" t="n">
+      <c r="G34" s="19" t="n">
         <v>77.25</v>
       </c>
-      <c r="H34" s="22" t="n">
+      <c r="H34" s="19" t="n">
         <v>67.33</v>
       </c>
-      <c r="I34" s="22" t="n">
+      <c r="I34" s="19" t="n">
         <v>45.67</v>
       </c>
-      <c r="J34" s="22" t="n">
+      <c r="J34" s="19" t="n">
         <v>913.33</v>
       </c>
     </row>
@@ -12649,28 +13096,28 @@
           <t>介護老人福祉施設</t>
         </is>
       </c>
-      <c r="C38" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="22" t="n">
+      <c r="C38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="19" t="n">
         <v>5.98</v>
       </c>
-      <c r="F38" s="22" t="n">
+      <c r="F38" s="19" t="n">
         <v>19.16</v>
       </c>
-      <c r="G38" s="22" t="n">
+      <c r="G38" s="19" t="n">
         <v>45.1</v>
       </c>
-      <c r="H38" s="22" t="n">
+      <c r="H38" s="19" t="n">
         <v>48.51</v>
       </c>
-      <c r="I38" s="22" t="n">
+      <c r="I38" s="19" t="n">
         <v>25.84</v>
       </c>
-      <c r="J38" s="22" t="n">
+      <c r="J38" s="19" t="n">
         <v>144.59</v>
       </c>
     </row>
@@ -12683,28 +13130,28 @@
           <t>地域密着型介護老人福祉施設入所者生活介護</t>
         </is>
       </c>
-      <c r="C39" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="22" t="n">
+      <c r="C39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="19" t="n">
         <v>2.25</v>
       </c>
-      <c r="F39" s="22" t="n">
+      <c r="F39" s="19" t="n">
         <v>11.15</v>
       </c>
-      <c r="G39" s="22" t="n">
+      <c r="G39" s="19" t="n">
         <v>10.66</v>
       </c>
-      <c r="H39" s="22" t="n">
+      <c r="H39" s="19" t="n">
         <v>22.42</v>
       </c>
-      <c r="I39" s="22" t="n">
+      <c r="I39" s="19" t="n">
         <v>15.44</v>
       </c>
-      <c r="J39" s="22" t="n">
+      <c r="J39" s="19" t="n">
         <v>61.92</v>
       </c>
     </row>
@@ -12717,28 +13164,28 @@
           <t>介護老人保健施設</t>
         </is>
       </c>
-      <c r="C40" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="22" t="n">
+      <c r="C40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="19" t="n">
         <v>31.71</v>
       </c>
-      <c r="F40" s="22" t="n">
+      <c r="F40" s="19" t="n">
         <v>32.31</v>
       </c>
-      <c r="G40" s="22" t="n">
+      <c r="G40" s="19" t="n">
         <v>26.75</v>
       </c>
-      <c r="H40" s="22" t="n">
+      <c r="H40" s="19" t="n">
         <v>34.72</v>
       </c>
-      <c r="I40" s="22" t="n">
+      <c r="I40" s="19" t="n">
         <v>14.57</v>
       </c>
-      <c r="J40" s="22" t="n">
+      <c r="J40" s="19" t="n">
         <v>140.06</v>
       </c>
     </row>
@@ -12751,28 +13198,28 @@
           <t>介護医療院</t>
         </is>
       </c>
-      <c r="C41" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="22" t="n">
+      <c r="C41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="19" t="n">
         <v>0.09</v>
       </c>
-      <c r="I41" s="22" t="n">
+      <c r="I41" s="19" t="n">
         <v>5.64</v>
       </c>
-      <c r="J41" s="22" t="n">
+      <c r="J41" s="19" t="n">
         <v>5.72</v>
       </c>
     </row>
@@ -12785,28 +13232,28 @@
           <t>介護療養型医療施設</t>
         </is>
       </c>
-      <c r="C42" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="22" t="n">
+      <c r="C42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12819,28 +13266,28 @@
           <t>特定施設入居者生活介護</t>
         </is>
       </c>
-      <c r="C43" s="22" t="n">
+      <c r="C43" s="19" t="n">
         <v>8.31</v>
       </c>
-      <c r="D43" s="22" t="n">
+      <c r="D43" s="19" t="n">
         <v>5.54</v>
       </c>
-      <c r="E43" s="22" t="n">
+      <c r="E43" s="19" t="n">
         <v>15.51</v>
       </c>
-      <c r="F43" s="22" t="n">
+      <c r="F43" s="19" t="n">
         <v>8.359999999999999</v>
       </c>
-      <c r="G43" s="22" t="n">
+      <c r="G43" s="19" t="n">
         <v>8.57</v>
       </c>
-      <c r="H43" s="22" t="n">
+      <c r="H43" s="19" t="n">
         <v>11.25</v>
       </c>
-      <c r="I43" s="22" t="n">
+      <c r="I43" s="19" t="n">
         <v>6.59</v>
       </c>
-      <c r="J43" s="22" t="n">
+      <c r="J43" s="19" t="n">
         <v>64.13</v>
       </c>
     </row>
@@ -12853,28 +13300,28 @@
           <t>地域密着型特定施設入居者生活介護</t>
         </is>
       </c>
-      <c r="C44" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="22" t="n">
+      <c r="C44" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12887,28 +13334,28 @@
           <t>認知症対応型共同生活介護</t>
         </is>
       </c>
-      <c r="C45" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="22" t="n">
+      <c r="C45" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="19" t="n">
         <v>0.43</v>
       </c>
-      <c r="E45" s="22" t="n">
+      <c r="E45" s="19" t="n">
         <v>12.48</v>
       </c>
-      <c r="F45" s="22" t="n">
+      <c r="F45" s="19" t="n">
         <v>19.51</v>
       </c>
-      <c r="G45" s="22" t="n">
+      <c r="G45" s="19" t="n">
         <v>22.81</v>
       </c>
-      <c r="H45" s="22" t="n">
+      <c r="H45" s="19" t="n">
         <v>15.7</v>
       </c>
-      <c r="I45" s="22" t="n">
+      <c r="I45" s="19" t="n">
         <v>14.31</v>
       </c>
-      <c r="J45" s="22" t="n">
+      <c r="J45" s="19" t="n">
         <v>85.23999999999999</v>
       </c>
     </row>
@@ -12921,28 +13368,28 @@
           <t>訪問介護</t>
         </is>
       </c>
-      <c r="C46" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="22" t="n">
+      <c r="C46" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="19" t="n">
         <v>103.89</v>
       </c>
-      <c r="F46" s="22" t="n">
+      <c r="F46" s="19" t="n">
         <v>51.9</v>
       </c>
-      <c r="G46" s="22" t="n">
+      <c r="G46" s="19" t="n">
         <v>44.66</v>
       </c>
-      <c r="H46" s="22" t="n">
+      <c r="H46" s="19" t="n">
         <v>46.5</v>
       </c>
-      <c r="I46" s="22" t="n">
+      <c r="I46" s="19" t="n">
         <v>34.86</v>
       </c>
-      <c r="J46" s="22" t="n">
+      <c r="J46" s="19" t="n">
         <v>281.83</v>
       </c>
     </row>
@@ -12955,28 +13402,28 @@
           <t>訪問入浴介護</t>
         </is>
       </c>
-      <c r="C47" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="22" t="n">
+      <c r="C47" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="19" t="n">
         <v>1.21</v>
       </c>
-      <c r="F47" s="22" t="n">
+      <c r="F47" s="19" t="n">
         <v>0.26</v>
       </c>
-      <c r="G47" s="22" t="n">
+      <c r="G47" s="19" t="n">
         <v>0.26</v>
       </c>
-      <c r="H47" s="22" t="n">
+      <c r="H47" s="19" t="n">
         <v>1.22</v>
       </c>
-      <c r="I47" s="22" t="n">
+      <c r="I47" s="19" t="n">
         <v>2.52</v>
       </c>
-      <c r="J47" s="22" t="n">
+      <c r="J47" s="19" t="n">
         <v>5.47</v>
       </c>
     </row>
@@ -12989,28 +13436,28 @@
           <t>訪問看護</t>
         </is>
       </c>
-      <c r="C48" s="22" t="n">
+      <c r="C48" s="19" t="n">
         <v>10.64</v>
       </c>
-      <c r="D48" s="22" t="n">
+      <c r="D48" s="19" t="n">
         <v>14.72</v>
       </c>
-      <c r="E48" s="22" t="n">
+      <c r="E48" s="19" t="n">
         <v>42.72</v>
       </c>
-      <c r="F48" s="22" t="n">
+      <c r="F48" s="19" t="n">
         <v>26.56</v>
       </c>
-      <c r="G48" s="22" t="n">
+      <c r="G48" s="19" t="n">
         <v>14.51</v>
       </c>
-      <c r="H48" s="22" t="n">
+      <c r="H48" s="19" t="n">
         <v>15.88</v>
       </c>
-      <c r="I48" s="22" t="n">
+      <c r="I48" s="19" t="n">
         <v>15.87</v>
       </c>
-      <c r="J48" s="22" t="n">
+      <c r="J48" s="19" t="n">
         <v>140.9</v>
       </c>
     </row>
@@ -13023,28 +13470,28 @@
           <t>訪問リハビリテーション</t>
         </is>
       </c>
-      <c r="C49" s="22" t="n">
+      <c r="C49" s="19" t="n">
         <v>3.29</v>
       </c>
-      <c r="D49" s="22" t="n">
+      <c r="D49" s="19" t="n">
         <v>10.74</v>
       </c>
-      <c r="E49" s="22" t="n">
+      <c r="E49" s="19" t="n">
         <v>21.06</v>
       </c>
-      <c r="F49" s="22" t="n">
+      <c r="F49" s="19" t="n">
         <v>17.59</v>
       </c>
-      <c r="G49" s="22" t="n">
+      <c r="G49" s="19" t="n">
         <v>8.220000000000001</v>
       </c>
-      <c r="H49" s="22" t="n">
+      <c r="H49" s="19" t="n">
         <v>4.01</v>
       </c>
-      <c r="I49" s="22" t="n">
+      <c r="I49" s="19" t="n">
         <v>4.86</v>
       </c>
-      <c r="J49" s="22" t="n">
+      <c r="J49" s="19" t="n">
         <v>69.76000000000001</v>
       </c>
     </row>
@@ -13057,28 +13504,28 @@
           <t>居宅療養管理指導</t>
         </is>
       </c>
-      <c r="C50" s="22" t="n">
+      <c r="C50" s="19" t="n">
         <v>7.27</v>
       </c>
-      <c r="D50" s="22" t="n">
+      <c r="D50" s="19" t="n">
         <v>7.27</v>
       </c>
-      <c r="E50" s="22" t="n">
+      <c r="E50" s="19" t="n">
         <v>38.99</v>
       </c>
-      <c r="F50" s="22" t="n">
+      <c r="F50" s="19" t="n">
         <v>32.48</v>
       </c>
-      <c r="G50" s="22" t="n">
+      <c r="G50" s="19" t="n">
         <v>39.33</v>
       </c>
-      <c r="H50" s="22" t="n">
+      <c r="H50" s="19" t="n">
         <v>41.7</v>
       </c>
-      <c r="I50" s="22" t="n">
+      <c r="I50" s="19" t="n">
         <v>34.69</v>
       </c>
-      <c r="J50" s="22" t="n">
+      <c r="J50" s="19" t="n">
         <v>201.74</v>
       </c>
     </row>
@@ -13091,28 +13538,28 @@
           <t>通所介護</t>
         </is>
       </c>
-      <c r="C51" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="22" t="n">
+      <c r="C51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="19" t="n">
         <v>51.64</v>
       </c>
-      <c r="F51" s="22" t="n">
+      <c r="F51" s="19" t="n">
         <v>23.08</v>
       </c>
-      <c r="G51" s="22" t="n">
+      <c r="G51" s="19" t="n">
         <v>11.28</v>
       </c>
-      <c r="H51" s="22" t="n">
+      <c r="H51" s="19" t="n">
         <v>12.21</v>
       </c>
-      <c r="I51" s="22" t="n">
+      <c r="I51" s="19" t="n">
         <v>3.3</v>
       </c>
-      <c r="J51" s="22" t="n">
+      <c r="J51" s="19" t="n">
         <v>101.51</v>
       </c>
     </row>
@@ -13125,28 +13572,28 @@
           <t>地域密着型通所介護</t>
         </is>
       </c>
-      <c r="C52" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="22" t="n">
+      <c r="C52" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="19" t="n">
         <v>38.56</v>
       </c>
-      <c r="F52" s="22" t="n">
+      <c r="F52" s="19" t="n">
         <v>24.65</v>
       </c>
-      <c r="G52" s="22" t="n">
+      <c r="G52" s="19" t="n">
         <v>9.09</v>
       </c>
-      <c r="H52" s="22" t="n">
+      <c r="H52" s="19" t="n">
         <v>4.01</v>
       </c>
-      <c r="I52" s="22" t="n">
+      <c r="I52" s="19" t="n">
         <v>3.12</v>
       </c>
-      <c r="J52" s="22" t="n">
+      <c r="J52" s="19" t="n">
         <v>79.43000000000001</v>
       </c>
     </row>
@@ -13159,28 +13606,28 @@
           <t>通所リハビリテーション</t>
         </is>
       </c>
-      <c r="C53" s="22" t="n">
+      <c r="C53" s="19" t="n">
         <v>32.36</v>
       </c>
-      <c r="D53" s="22" t="n">
+      <c r="D53" s="19" t="n">
         <v>54.29</v>
       </c>
-      <c r="E53" s="22" t="n">
+      <c r="E53" s="19" t="n">
         <v>101.64</v>
       </c>
-      <c r="F53" s="22" t="n">
+      <c r="F53" s="19" t="n">
         <v>54.26</v>
       </c>
-      <c r="G53" s="22" t="n">
+      <c r="G53" s="19" t="n">
         <v>20.98</v>
       </c>
-      <c r="H53" s="22" t="n">
+      <c r="H53" s="19" t="n">
         <v>14.13</v>
       </c>
-      <c r="I53" s="22" t="n">
+      <c r="I53" s="19" t="n">
         <v>6.94</v>
       </c>
-      <c r="J53" s="22" t="n">
+      <c r="J53" s="19" t="n">
         <v>284.6</v>
       </c>
     </row>
@@ -13193,28 +13640,28 @@
           <t>短期入所生活介護</t>
         </is>
       </c>
-      <c r="C54" s="22" t="n">
+      <c r="C54" s="19" t="n">
         <v>0.61</v>
       </c>
-      <c r="D54" s="22" t="n">
+      <c r="D54" s="19" t="n">
         <v>0.95</v>
       </c>
-      <c r="E54" s="22" t="n">
+      <c r="E54" s="19" t="n">
         <v>6.67</v>
       </c>
-      <c r="F54" s="22" t="n">
+      <c r="F54" s="19" t="n">
         <v>10.89</v>
       </c>
-      <c r="G54" s="22" t="n">
+      <c r="G54" s="19" t="n">
         <v>3.58</v>
       </c>
-      <c r="H54" s="22" t="n">
+      <c r="H54" s="19" t="n">
         <v>3.66</v>
       </c>
-      <c r="I54" s="22" t="n">
+      <c r="I54" s="19" t="n">
         <v>1.3</v>
       </c>
-      <c r="J54" s="22" t="n">
+      <c r="J54" s="19" t="n">
         <v>27.66</v>
       </c>
     </row>
@@ -13227,28 +13674,28 @@
           <t>短期入所療養介護（老健）</t>
         </is>
       </c>
-      <c r="C55" s="22" t="n">
+      <c r="C55" s="19" t="n">
         <v>0.43</v>
       </c>
-      <c r="D55" s="22" t="n">
+      <c r="D55" s="19" t="n">
         <v>0.09</v>
       </c>
-      <c r="E55" s="22" t="n">
+      <c r="E55" s="19" t="n">
         <v>2.95</v>
       </c>
-      <c r="F55" s="22" t="n">
+      <c r="F55" s="19" t="n">
         <v>5.4</v>
       </c>
-      <c r="G55" s="22" t="n">
+      <c r="G55" s="19" t="n">
         <v>2.88</v>
       </c>
-      <c r="H55" s="22" t="n">
+      <c r="H55" s="19" t="n">
         <v>4.36</v>
       </c>
-      <c r="I55" s="22" t="n">
+      <c r="I55" s="19" t="n">
         <v>1.21</v>
       </c>
-      <c r="J55" s="22" t="n">
+      <c r="J55" s="19" t="n">
         <v>17.33</v>
       </c>
     </row>
@@ -13261,28 +13708,28 @@
           <t>短期入所療養介護（病院等）</t>
         </is>
       </c>
-      <c r="C56" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="22" t="n">
+      <c r="C56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13295,28 +13742,28 @@
           <t>短期入所療養介護（介護医療院）</t>
         </is>
       </c>
-      <c r="C57" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="22" t="n">
+      <c r="C57" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13329,28 +13776,28 @@
           <t>福祉用具貸与</t>
         </is>
       </c>
-      <c r="C58" s="22" t="n">
+      <c r="C58" s="19" t="n">
         <v>68.79000000000001</v>
       </c>
-      <c r="D58" s="22" t="n">
+      <c r="D58" s="19" t="n">
         <v>123.39</v>
       </c>
-      <c r="E58" s="22" t="n">
+      <c r="E58" s="19" t="n">
         <v>184.56</v>
       </c>
-      <c r="F58" s="22" t="n">
+      <c r="F58" s="19" t="n">
         <v>128.54</v>
       </c>
-      <c r="G58" s="22" t="n">
+      <c r="G58" s="19" t="n">
         <v>69.14</v>
       </c>
-      <c r="H58" s="22" t="n">
+      <c r="H58" s="19" t="n">
         <v>52</v>
       </c>
-      <c r="I58" s="22" t="n">
+      <c r="I58" s="19" t="n">
         <v>42.67</v>
       </c>
-      <c r="J58" s="22" t="n">
+      <c r="J58" s="19" t="n">
         <v>669.09</v>
       </c>
     </row>
@@ -13363,28 +13810,28 @@
           <t>特定福祉用具販売</t>
         </is>
       </c>
-      <c r="C59" s="22" t="n">
+      <c r="C59" s="19" t="n">
         <v>1.73</v>
       </c>
-      <c r="D59" s="22" t="n">
+      <c r="D59" s="19" t="n">
         <v>2.16</v>
       </c>
-      <c r="E59" s="22" t="n">
+      <c r="E59" s="19" t="n">
         <v>3.64</v>
       </c>
-      <c r="F59" s="22" t="n">
+      <c r="F59" s="19" t="n">
         <v>2.26</v>
       </c>
-      <c r="G59" s="22" t="n">
+      <c r="G59" s="19" t="n">
         <v>0.7</v>
       </c>
-      <c r="H59" s="22" t="n">
+      <c r="H59" s="19" t="n">
         <v>0.52</v>
       </c>
-      <c r="I59" s="22" t="n">
+      <c r="I59" s="19" t="n">
         <v>0.17</v>
       </c>
-      <c r="J59" s="22" t="n">
+      <c r="J59" s="19" t="n">
         <v>11.19</v>
       </c>
     </row>
@@ -13397,28 +13844,28 @@
           <t>住宅改修</t>
         </is>
       </c>
-      <c r="C60" s="22" t="n">
+      <c r="C60" s="19" t="n">
         <v>2.34</v>
       </c>
-      <c r="D60" s="22" t="n">
+      <c r="D60" s="19" t="n">
         <v>1.65</v>
       </c>
-      <c r="E60" s="22" t="n">
+      <c r="E60" s="19" t="n">
         <v>2.43</v>
       </c>
-      <c r="F60" s="22" t="n">
+      <c r="F60" s="19" t="n">
         <v>1.31</v>
       </c>
-      <c r="G60" s="22" t="n">
+      <c r="G60" s="19" t="n">
         <v>0.61</v>
       </c>
-      <c r="H60" s="22" t="n">
+      <c r="H60" s="19" t="n">
         <v>0.17</v>
       </c>
-      <c r="I60" s="22" t="n">
+      <c r="I60" s="19" t="n">
         <v>0.26</v>
       </c>
-      <c r="J60" s="22" t="n">
+      <c r="J60" s="19" t="n">
         <v>8.76</v>
       </c>
     </row>
@@ -13431,28 +13878,28 @@
           <t>定期巡回・随時対応型訪問介護看護</t>
         </is>
       </c>
-      <c r="C61" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="22" t="n">
+      <c r="C61" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="19" t="n">
         <v>0.26</v>
       </c>
-      <c r="F61" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" s="22" t="n">
+      <c r="F61" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="19" t="n">
         <v>0.35</v>
       </c>
-      <c r="J61" s="22" t="n">
+      <c r="J61" s="19" t="n">
         <v>0.61</v>
       </c>
     </row>
@@ -13465,28 +13912,28 @@
           <t>夜間対応型訪問介護</t>
         </is>
       </c>
-      <c r="C62" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="22" t="n">
+      <c r="C62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13499,28 +13946,28 @@
           <t>認知症対応型通所介護</t>
         </is>
       </c>
-      <c r="C63" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="22" t="n">
+      <c r="C63" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="19" t="n">
         <v>1.05</v>
       </c>
-      <c r="G63" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="22" t="n">
+      <c r="G63" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="19" t="n">
         <v>1.05</v>
       </c>
     </row>
@@ -13533,28 +13980,28 @@
           <t>小規模多機能型居宅介護</t>
         </is>
       </c>
-      <c r="C64" s="22" t="n">
+      <c r="C64" s="19" t="n">
         <v>4.33</v>
       </c>
-      <c r="D64" s="22" t="n">
+      <c r="D64" s="19" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="E64" s="22" t="n">
+      <c r="E64" s="19" t="n">
         <v>39.25</v>
       </c>
-      <c r="F64" s="22" t="n">
+      <c r="F64" s="19" t="n">
         <v>24.12</v>
       </c>
-      <c r="G64" s="22" t="n">
+      <c r="G64" s="19" t="n">
         <v>18.01</v>
       </c>
-      <c r="H64" s="22" t="n">
+      <c r="H64" s="19" t="n">
         <v>3.49</v>
       </c>
-      <c r="I64" s="22" t="n">
+      <c r="I64" s="19" t="n">
         <v>5.29</v>
       </c>
-      <c r="J64" s="22" t="n">
+      <c r="J64" s="19" t="n">
         <v>104.19</v>
       </c>
     </row>
@@ -13567,28 +14014,28 @@
           <t>看護小規模多機能型居宅介護</t>
         </is>
       </c>
-      <c r="C65" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D65" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="22" t="n">
+      <c r="C65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13601,28 +14048,28 @@
           <t>介護予防支援・居宅介護支援</t>
         </is>
       </c>
-      <c r="C66" s="22" t="n">
+      <c r="C66" s="19" t="n">
         <v>104.09</v>
       </c>
-      <c r="D66" s="22" t="n">
+      <c r="D66" s="19" t="n">
         <v>162.79</v>
       </c>
-      <c r="E66" s="22" t="n">
+      <c r="E66" s="19" t="n">
         <v>310.46</v>
       </c>
-      <c r="F66" s="22" t="n">
+      <c r="F66" s="19" t="n">
         <v>175.14</v>
       </c>
-      <c r="G66" s="22" t="n">
+      <c r="G66" s="19" t="n">
         <v>81.03</v>
       </c>
-      <c r="H66" s="22" t="n">
+      <c r="H66" s="19" t="n">
         <v>70.48999999999999</v>
       </c>
-      <c r="I66" s="22" t="n">
+      <c r="I66" s="19" t="n">
         <v>47.53</v>
       </c>
-      <c r="J66" s="22" t="n">
+      <c r="J66" s="19" t="n">
         <v>951.52</v>
       </c>
     </row>
@@ -13633,28 +14080,28 @@
           <t>計</t>
         </is>
       </c>
-      <c r="C67" s="23" t="n">
+      <c r="C67" s="26" t="n">
         <v>244.17</v>
       </c>
-      <c r="D67" s="23" t="n">
+      <c r="D67" s="26" t="n">
         <v>393.72</v>
       </c>
-      <c r="E67" s="23" t="n">
+      <c r="E67" s="26" t="n">
         <v>1017.86</v>
       </c>
-      <c r="F67" s="23" t="n">
+      <c r="F67" s="26" t="n">
         <v>669.97</v>
       </c>
-      <c r="G67" s="23" t="n">
+      <c r="G67" s="26" t="n">
         <v>438.17</v>
       </c>
-      <c r="H67" s="23" t="n">
+      <c r="H67" s="26" t="n">
         <v>407.07</v>
       </c>
-      <c r="I67" s="23" t="n">
+      <c r="I67" s="26" t="n">
         <v>287.33</v>
       </c>
-      <c r="J67" s="23" t="n">
+      <c r="J67" s="26" t="n">
         <v>3458.3</v>
       </c>
     </row>
@@ -13789,7 +14236,7 @@
       <c r="G6" s="18" t="n">
         <v>55.4091</v>
       </c>
-      <c r="H6" s="24" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -13826,7 +14273,7 @@
       <c r="G7" s="18" t="n">
         <v>6.2857</v>
       </c>
-      <c r="H7" s="24" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -13859,7 +14306,7 @@
       <c r="G8" s="18" t="n">
         <v>8.7803</v>
       </c>
-      <c r="H8" s="24" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -13892,7 +14339,7 @@
       <c r="G9" s="18" t="n">
         <v>11.688</v>
       </c>
-      <c r="H9" s="24" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -13929,7 +14376,7 @@
       <c r="G10" s="18" t="n">
         <v>8.738899999999999</v>
       </c>
-      <c r="H10" s="24" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -13966,7 +14413,7 @@
       <c r="G11" s="18" t="n">
         <v>7.8862</v>
       </c>
-      <c r="H11" s="24" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -14003,7 +14450,7 @@
       <c r="G12" s="18" t="n">
         <v>7.1326</v>
       </c>
-      <c r="H12" s="24" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -14036,7 +14483,7 @@
       <c r="G13" s="18" t="n">
         <v>11.7733</v>
       </c>
-      <c r="H13" s="24" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -14069,7 +14516,7 @@
       <c r="G14" s="18" t="n">
         <v>6.1399</v>
       </c>
-      <c r="H14" s="24" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -14110,7 +14557,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="H15" s="24" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -14151,7 +14598,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="H16" s="24" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -14188,7 +14635,7 @@
       <c r="G17" s="18" t="n">
         <v>7.9167</v>
       </c>
-      <c r="H17" s="24" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -14278,7 +14725,7 @@
       <c r="G22" s="15" t="n">
         <v>15629.2</v>
       </c>
-      <c r="H22" s="19" t="n">
+      <c r="H22" s="23" t="n">
         <v>1.044</v>
       </c>
       <c r="I22" s="6" t="inlineStr"/>
@@ -14309,7 +14756,7 @@
       <c r="G23" s="15" t="n">
         <v>34.4</v>
       </c>
-      <c r="H23" s="19" t="n">
+      <c r="H23" s="23" t="n">
         <v>1.042</v>
       </c>
       <c r="I23" s="6" t="inlineStr"/>
@@ -14340,7 +14787,7 @@
       <c r="G24" s="15" t="n">
         <v>1122.3</v>
       </c>
-      <c r="H24" s="19" t="n">
+      <c r="H24" s="23" t="n">
         <v>1.043</v>
       </c>
       <c r="I24" s="6" t="inlineStr"/>
@@ -14371,7 +14818,7 @@
       <c r="G25" s="15" t="n">
         <v>797.4</v>
       </c>
-      <c r="H25" s="19" t="n">
+      <c r="H25" s="23" t="n">
         <v>1.043</v>
       </c>
       <c r="I25" s="6" t="inlineStr"/>
@@ -14402,7 +14849,7 @@
       <c r="G26" s="15" t="n">
         <v>887.2</v>
       </c>
-      <c r="H26" s="19" t="n">
+      <c r="H26" s="23" t="n">
         <v>1.043</v>
       </c>
       <c r="I26" s="6" t="inlineStr"/>
@@ -14433,7 +14880,7 @@
       <c r="G27" s="15" t="n">
         <v>626.7</v>
       </c>
-      <c r="H27" s="19" t="n">
+      <c r="H27" s="23" t="n">
         <v>1.043</v>
       </c>
       <c r="I27" s="6" t="inlineStr"/>
@@ -14464,7 +14911,7 @@
       <c r="G28" s="15" t="n">
         <v>1412.2</v>
       </c>
-      <c r="H28" s="19" t="n">
+      <c r="H28" s="23" t="n">
         <v>1.043</v>
       </c>
       <c r="I28" s="6" t="inlineStr"/>
@@ -14495,7 +14942,7 @@
       <c r="G29" s="15" t="n">
         <v>319.7</v>
       </c>
-      <c r="H29" s="19" t="n">
+      <c r="H29" s="23" t="n">
         <v>1.044</v>
       </c>
       <c r="I29" s="6" t="inlineStr"/>
@@ -14526,7 +14973,7 @@
       <c r="G30" s="15" t="n">
         <v>105.1</v>
       </c>
-      <c r="H30" s="19" t="n">
+      <c r="H30" s="23" t="n">
         <v>1.045</v>
       </c>
       <c r="I30" s="6" t="inlineStr"/>
@@ -14623,7 +15070,7 @@
       <c r="G33" s="15" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="H33" s="19" t="n">
+      <c r="H33" s="23" t="n">
         <v>1.045</v>
       </c>
       <c r="I33" s="6" t="inlineStr"/>
@@ -18461,12 +18908,12 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>単価固定（06シート）</t>
+          <t>要介護度計の単価による場合</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>要介護度別の単価</t>
+          <t>要介護度別の単価（本表の採用）</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -18499,22 +18946,22 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
+          <t>2,978,267,893</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
           <t>2,978,975,041</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>2,978,975,041</t>
-        </is>
-      </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>707,147</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>+0.000％</t>
+          <t>+0.024％</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr"/>
@@ -18537,22 +18984,22 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
+          <t>3,010,470,894</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
           <t>3,011,540,164</t>
         </is>
       </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>3,011,540,164</t>
-        </is>
-      </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1,069,271</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>+0.000％</t>
+          <t>+0.036％</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr"/>
@@ -18575,22 +19022,22 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
+          <t>3,043,161,657</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
           <t>3,044,598,937</t>
         </is>
       </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>3,044,598,937</t>
-        </is>
-      </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1,437,280</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>+0.000％</t>
+          <t>+0.047％</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr"/>
@@ -18603,7 +19050,7 @@
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="25" t="n">
+      <c r="A63" s="27" t="n">
         <v>4</v>
       </c>
       <c r="B63" s="16" t="inlineStr">
@@ -18613,22 +19060,22 @@
       </c>
       <c r="C63" s="16" t="inlineStr">
         <is>
+          <t>3,066,588,037</t>
+        </is>
+      </c>
+      <c r="D63" s="16" t="inlineStr">
+        <is>
           <t>3,068,203,871</t>
         </is>
       </c>
-      <c r="D63" s="16" t="inlineStr">
-        <is>
-          <t>3,068,203,871</t>
-        </is>
-      </c>
       <c r="E63" s="16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1,615,834</t>
         </is>
       </c>
       <c r="F63" s="16" t="inlineStr">
         <is>
-          <t>+0.000％</t>
+          <t>+0.053％</t>
         </is>
       </c>
       <c r="G63" s="16" t="inlineStr"/>
@@ -18641,7 +19088,7 @@
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="25" t="n">
+      <c r="A64" s="27" t="n">
         <v>5</v>
       </c>
       <c r="B64" s="16" t="inlineStr">
@@ -18651,22 +19098,22 @@
       </c>
       <c r="C64" s="16" t="inlineStr">
         <is>
+          <t>3,310,122,835</t>
+        </is>
+      </c>
+      <c r="D64" s="16" t="inlineStr">
+        <is>
           <t>3,317,848,527</t>
         </is>
       </c>
-      <c r="D64" s="16" t="inlineStr">
-        <is>
-          <t>3,317,848,527</t>
-        </is>
-      </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7,725,692</t>
         </is>
       </c>
       <c r="F64" s="16" t="inlineStr">
         <is>
-          <t>+0.000％</t>
+          <t>+0.233％</t>
         </is>
       </c>
       <c r="G64" s="16" t="inlineStr"/>
@@ -18679,7 +19126,7 @@
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="25" t="n">
+      <c r="A65" s="27" t="n">
         <v>6</v>
       </c>
       <c r="B65" s="16" t="inlineStr">
@@ -18689,22 +19136,22 @@
       </c>
       <c r="C65" s="16" t="inlineStr">
         <is>
+          <t>3,408,932,536</t>
+        </is>
+      </c>
+      <c r="D65" s="16" t="inlineStr">
+        <is>
           <t>3,418,469,468</t>
         </is>
       </c>
-      <c r="D65" s="16" t="inlineStr">
-        <is>
-          <t>3,418,469,468</t>
-        </is>
-      </c>
       <c r="E65" s="16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9,536,931</t>
         </is>
       </c>
       <c r="F65" s="16" t="inlineStr">
         <is>
-          <t>+0.000％</t>
+          <t>+0.280％</t>
         </is>
       </c>
       <c r="G65" s="16" t="inlineStr"/>
@@ -18717,7 +19164,7 @@
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
-      <c r="A66" s="25" t="n">
+      <c r="A66" s="27" t="n">
         <v>7</v>
       </c>
       <c r="B66" s="16" t="inlineStr">
@@ -18727,22 +19174,22 @@
       </c>
       <c r="C66" s="16" t="inlineStr">
         <is>
+          <t>3,258,825,048</t>
+        </is>
+      </c>
+      <c r="D66" s="16" t="inlineStr">
+        <is>
           <t>3,265,402,536</t>
         </is>
       </c>
-      <c r="D66" s="16" t="inlineStr">
-        <is>
-          <t>3,265,402,536</t>
-        </is>
-      </c>
       <c r="E66" s="16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6,577,487</t>
         </is>
       </c>
       <c r="F66" s="16" t="inlineStr">
         <is>
-          <t>+0.000％</t>
+          <t>+0.202％</t>
         </is>
       </c>
       <c r="G66" s="16" t="inlineStr"/>
@@ -18755,7 +19202,7 @@
       </c>
     </row>
     <row r="67" ht="22" customHeight="1">
-      <c r="A67" s="25" t="n">
+      <c r="A67" s="27" t="n">
         <v>8</v>
       </c>
       <c r="B67" s="16" t="inlineStr">
@@ -18765,22 +19212,22 @@
       </c>
       <c r="C67" s="16" t="inlineStr">
         <is>
+          <t>3,240,335,214</t>
+        </is>
+      </c>
+      <c r="D67" s="16" t="inlineStr">
+        <is>
           <t>3,245,610,859</t>
         </is>
       </c>
-      <c r="D67" s="16" t="inlineStr">
-        <is>
-          <t>3,245,610,859</t>
-        </is>
-      </c>
       <c r="E67" s="16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5,275,646</t>
         </is>
       </c>
       <c r="F67" s="16" t="inlineStr">
         <is>
-          <t>+0.000％</t>
+          <t>+0.163％</t>
         </is>
       </c>
       <c r="G67" s="16" t="inlineStr"/>
@@ -18792,12 +19239,12 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="68" customHeight="1">
+    <row r="68" ht="84" customHeight="1">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>注1）06シートは種別ごとの単価（延べ1人あたり）を令和7年度で固定しています。要介護度別の単価を用いると、要介護度の構成が重度側へ動く分だけ平均の単価が上がります。
-注2）効きは第10期では小さく（令和11年度で+0.000％）、算定上の月額基準額で+0.0円です。令和22年度では+0.000％に開きます。
-注3）本表の採用値は06シート（単価固定）のままとしています。ツールの要介護度別の値は3町合計であり、要介護度間の比が保険者単位でも同じであることを確かめられていないためです。［要確認］</t>
+          <t>注1）左の列は、総括表詳細（４）の種別ごとの単価（要介護度計の延べ1人あたり）を令和7年度で固定した場合の給付費です。右の列は要介護度別の単価によるもので、要介護度の構成が重度側へ動く分だけ平均の単価が上がります。
+注2）効きは第10期では小さく（令和11年度で+0.047％）、算定上の月額基準額で+2.16円です。令和22年度では+0.280％に開きます。
+注3）本表の採用値は右の列（要介護度別の単価）です。要介護度間の比は給付費データ（保険者単位）によるものであり、年報の利用者数で加重した平均が総括表詳細（４）の単価と一致するよう比例調整しているため、基準年度では総括表の給付費を円単位で再現します（点検16）。左の列は対照のために掲げるものです。</t>
         </is>
       </c>
     </row>
@@ -18894,7 +19341,7 @@
           <t>総括表詳細（２）　利用者数の割合</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>第1号被保険者数</t>
         </is>
@@ -18926,7 +19373,7 @@
           <t>管理指標グラフ D32　受給率</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>第1号被保険者数</t>
         </is>
@@ -18990,7 +19437,7 @@
           <t>将来推計　施設・居住系サービス利用率</t>
         </is>
       </c>
-      <c r="C9" s="27" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>認定者数（推定）</t>
         </is>
@@ -19052,7 +19499,7 @@
           <t>介護予防支援・居宅介護支援</t>
         </is>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C12" s="19" t="n">
         <v>913.33</v>
       </c>
       <c r="D12" s="18" t="n">
@@ -19074,7 +19521,7 @@
           <t>福祉用具貸与</t>
         </is>
       </c>
-      <c r="C13" s="22" t="n">
+      <c r="C13" s="19" t="n">
         <v>642.08</v>
       </c>
       <c r="D13" s="18" t="n">
@@ -19096,7 +19543,7 @@
           <t>通所リハビリテーション</t>
         </is>
       </c>
-      <c r="C14" s="22" t="n">
+      <c r="C14" s="19" t="n">
         <v>273.25</v>
       </c>
       <c r="D14" s="18" t="n">
@@ -19118,7 +19565,7 @@
           <t>訪問介護</t>
         </is>
       </c>
-      <c r="C15" s="22" t="n">
+      <c r="C15" s="19" t="n">
         <v>270.08</v>
       </c>
       <c r="D15" s="18" t="n">
@@ -19140,7 +19587,7 @@
           <t>居宅療養管理指導</t>
         </is>
       </c>
-      <c r="C16" s="22" t="n">
+      <c r="C16" s="19" t="n">
         <v>193.25</v>
       </c>
       <c r="D16" s="18" t="n">
@@ -19162,7 +19609,7 @@
           <t>訪問看護</t>
         </is>
       </c>
-      <c r="C17" s="22" t="n">
+      <c r="C17" s="19" t="n">
         <v>135.17</v>
       </c>
       <c r="D17" s="18" t="n">
@@ -19184,7 +19631,7 @@
           <t>小規模多機能型居宅介護</t>
         </is>
       </c>
-      <c r="C18" s="22" t="n">
+      <c r="C18" s="19" t="n">
         <v>99.92</v>
       </c>
       <c r="D18" s="18" t="n">
@@ -19206,7 +19653,7 @@
           <t>通所介護</t>
         </is>
       </c>
-      <c r="C19" s="22" t="n">
+      <c r="C19" s="19" t="n">
         <v>97.33</v>
       </c>
       <c r="D19" s="18" t="n">
@@ -19228,7 +19675,7 @@
           <t>地域密着型通所介護</t>
         </is>
       </c>
-      <c r="C20" s="22" t="n">
+      <c r="C20" s="19" t="n">
         <v>76.17</v>
       </c>
       <c r="D20" s="18" t="n">
@@ -19250,7 +19697,7 @@
           <t>訪問リハビリテーション</t>
         </is>
       </c>
-      <c r="C21" s="22" t="n">
+      <c r="C21" s="19" t="n">
         <v>66.92</v>
       </c>
       <c r="D21" s="18" t="n">
